--- a/assets/Benchmarking.xlsx
+++ b/assets/Benchmarking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO NO BORRAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO NO BORRAR\Documents\GitHub\asesores\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED4C25B-77AA-4F37-8867-CF4074D06145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363008FC-35CB-42BC-86E0-A3A48175F96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{F3156A63-ABA6-4DCB-AB8A-B4C8C83E2F35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{F3156A63-ABA6-4DCB-AB8A-B4C8C83E2F35}"/>
   </bookViews>
   <sheets>
     <sheet name="FILTRO" sheetId="9" r:id="rId1"/>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="473">
   <si>
     <t>Operador</t>
   </si>
@@ -650,9 +650,6 @@
     <t>HBO y WIN por 12 Meses</t>
   </si>
   <si>
-    <t>$89.900</t>
-  </si>
-  <si>
     <t>500 MG</t>
   </si>
   <si>
@@ -761,15 +758,9 @@
     <t>Monica Gutierrez</t>
   </si>
   <si>
-    <t>$119.900</t>
-  </si>
-  <si>
     <t>Doble TV+Internet</t>
   </si>
   <si>
-    <t>$63.700</t>
-  </si>
-  <si>
     <t>TV Avanzada</t>
   </si>
   <si>
@@ -1028,27 +1019,18 @@
     <t xml:space="preserve">Diney Acosta </t>
   </si>
   <si>
-    <t>$48000</t>
-  </si>
-  <si>
     <t>100MG</t>
   </si>
   <si>
     <t>DUO</t>
   </si>
   <si>
-    <t>$69.00</t>
-  </si>
-  <si>
     <t>150MG</t>
   </si>
   <si>
     <t>ESTRATO 1, 2 Y 4</t>
   </si>
   <si>
-    <t>$45000</t>
-  </si>
-  <si>
     <t>100GM</t>
   </si>
   <si>
@@ -1056,9 +1038,6 @@
   </si>
   <si>
     <t>ESTRATO 1, 2 Y 5</t>
-  </si>
-  <si>
-    <t>$56000</t>
   </si>
   <si>
     <t>250MG</t>
@@ -6221,13 +6200,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}" name="DatosHogar" displayName="DatosHogar" ref="C2:X169" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
-  <autoFilter ref="C2:X169" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Medellín y Área Metropolitana"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C2:X169" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{FF7CD40D-656D-4CDC-993A-13C9C7E8DB40}" name="Operador" dataDxfId="39"/>
     <tableColumn id="16" xr3:uid="{E9D94F91-8BF6-49E6-A3A2-E88FE2FF45B1}" name="Ciudad" dataDxfId="38"/>
@@ -7285,7 +7258,7 @@
         <v>88</v>
       </c>
       <c r="K2" s="54" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="L2" s="54" t="s">
         <v>89</v>
@@ -7315,7 +7288,7 @@
         <v>7</v>
       </c>
       <c r="U2" s="54" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="V2" s="54" t="s">
         <v>97</v>
@@ -8384,7 +8357,7 @@
         <v>134</v>
       </c>
       <c r="J18" s="57">
-        <v>119.9</v>
+        <v>119900</v>
       </c>
       <c r="K18" s="56" t="s">
         <v>145</v>
@@ -8449,8 +8422,8 @@
       <c r="I19" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="57" t="s">
-        <v>151</v>
+      <c r="J19" s="57">
+        <v>89900</v>
       </c>
       <c r="K19" s="56" t="s">
         <v>145</v>
@@ -8459,7 +8432,7 @@
         <v>146</v>
       </c>
       <c r="M19" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N19" s="56" t="s">
         <v>138</v>
@@ -8479,7 +8452,7 @@
         <v>1</v>
       </c>
       <c r="U19" s="58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V19" s="56" t="s">
         <v>139</v>
@@ -8525,7 +8498,7 @@
       </c>
       <c r="L20" s="56"/>
       <c r="M20" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N20" s="56" t="s">
         <v>148</v>
@@ -8589,7 +8562,7 @@
       </c>
       <c r="L21" s="56"/>
       <c r="M21" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N21" s="56" t="s">
         <v>138</v>
@@ -8607,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V21" s="56" t="s">
         <v>139</v>
@@ -8622,7 +8595,7 @@
         <v>46092</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="44" t="s">
         <v>30</v>
@@ -8655,7 +8628,7 @@
         <v>146</v>
       </c>
       <c r="M22" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N22" s="56" t="s">
         <v>148</v>
@@ -8688,7 +8661,7 @@
         <v>46092</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>30</v>
@@ -8721,7 +8694,7 @@
         <v>146</v>
       </c>
       <c r="M23" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N23" s="56" t="s">
         <v>138</v>
@@ -8739,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="U23" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V23" s="56" t="s">
         <v>139</v>
@@ -8754,7 +8727,7 @@
         <v>46092</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="44" t="s">
         <v>22</v>
@@ -8820,7 +8793,7 @@
         <v>46092</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="44" t="s">
         <v>22</v>
@@ -9034,7 +9007,7 @@
         <v>46092</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="44" t="s">
         <v>47</v>
@@ -9055,20 +9028,20 @@
         <v>24</v>
       </c>
       <c r="I28" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J28" s="57">
         <v>75000</v>
       </c>
       <c r="K28" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L28" s="56"/>
       <c r="M28" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="N28" s="56" t="s">
         <v>158</v>
-      </c>
-      <c r="N28" s="56" t="s">
-        <v>159</v>
       </c>
       <c r="O28" s="56">
         <v>130</v>
@@ -9095,7 +9068,7 @@
         <v>138</v>
       </c>
       <c r="W28" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X28" s="56" t="s">
         <v>21</v>
@@ -9127,20 +9100,20 @@
         <v>24</v>
       </c>
       <c r="I29" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J29" s="57">
         <v>75000</v>
       </c>
       <c r="K29" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L29" s="56"/>
       <c r="M29" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="N29" s="56" t="s">
         <v>158</v>
-      </c>
-      <c r="N29" s="56" t="s">
-        <v>159</v>
       </c>
       <c r="O29" s="56">
         <v>130</v>
@@ -9167,7 +9140,7 @@
         <v>138</v>
       </c>
       <c r="W29" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X29" s="56" t="s">
         <v>21</v>
@@ -9199,20 +9172,20 @@
         <v>24</v>
       </c>
       <c r="I30" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J30" s="57">
         <v>75000</v>
       </c>
       <c r="K30" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L30" s="56"/>
       <c r="M30" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="N30" s="56" t="s">
         <v>158</v>
-      </c>
-      <c r="N30" s="56" t="s">
-        <v>159</v>
       </c>
       <c r="O30" s="56">
         <v>130</v>
@@ -9239,7 +9212,7 @@
         <v>138</v>
       </c>
       <c r="W30" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X30" s="56" t="s">
         <v>21</v>
@@ -9250,7 +9223,7 @@
         <v>46092</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C31" s="44" t="s">
         <v>47</v>
@@ -9271,20 +9244,20 @@
         <v>32</v>
       </c>
       <c r="I31" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J31" s="57">
         <v>160000</v>
       </c>
       <c r="K31" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L31" s="56"/>
       <c r="M31" s="56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N31" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O31" s="56">
         <v>130</v>
@@ -9311,7 +9284,7 @@
         <v>138</v>
       </c>
       <c r="W31" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X31" s="56" t="s">
         <v>21</v>
@@ -9343,20 +9316,20 @@
         <v>32</v>
       </c>
       <c r="I32" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J32" s="57">
         <v>160000</v>
       </c>
       <c r="K32" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L32" s="56"/>
       <c r="M32" s="56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N32" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O32" s="56">
         <v>130</v>
@@ -9383,7 +9356,7 @@
         <v>138</v>
       </c>
       <c r="W32" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X32" s="56" t="s">
         <v>21</v>
@@ -9415,20 +9388,20 @@
         <v>32</v>
       </c>
       <c r="I33" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J33" s="57">
         <v>160000</v>
       </c>
       <c r="K33" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L33" s="56"/>
       <c r="M33" s="56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N33" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O33" s="56">
         <v>130</v>
@@ -9455,7 +9428,7 @@
         <v>138</v>
       </c>
       <c r="W33" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X33" s="56" t="s">
         <v>21</v>
@@ -9466,7 +9439,7 @@
         <v>46092</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>47</v>
@@ -9487,20 +9460,20 @@
         <v>17</v>
       </c>
       <c r="I34" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J34" s="57">
         <v>45000</v>
       </c>
       <c r="K34" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L34" s="56"/>
       <c r="M34" s="56" t="s">
         <v>138</v>
       </c>
       <c r="N34" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O34" s="56">
         <v>130</v>
@@ -9527,7 +9500,7 @@
         <v>138</v>
       </c>
       <c r="W34" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X34" s="56" t="s">
         <v>21</v>
@@ -9559,20 +9532,20 @@
         <v>17</v>
       </c>
       <c r="I35" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J35" s="57">
         <v>45000</v>
       </c>
       <c r="K35" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L35" s="56"/>
       <c r="M35" s="56" t="s">
         <v>138</v>
       </c>
       <c r="N35" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O35" s="56">
         <v>130</v>
@@ -9599,7 +9572,7 @@
         <v>138</v>
       </c>
       <c r="W35" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X35" s="56" t="s">
         <v>21</v>
@@ -9631,20 +9604,20 @@
         <v>17</v>
       </c>
       <c r="I36" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J36" s="57">
         <v>45000</v>
       </c>
       <c r="K36" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L36" s="56"/>
       <c r="M36" s="56" t="s">
         <v>138</v>
       </c>
       <c r="N36" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O36" s="56">
         <v>130</v>
@@ -9671,7 +9644,7 @@
         <v>138</v>
       </c>
       <c r="W36" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X36" s="56" t="s">
         <v>21</v>
@@ -9682,7 +9655,7 @@
         <v>46092</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>47</v>
@@ -9703,20 +9676,20 @@
         <v>24</v>
       </c>
       <c r="I37" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J37" s="57">
         <v>40000</v>
       </c>
       <c r="K37" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L37" s="56"/>
       <c r="M37" s="56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N37" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O37" s="56">
         <v>80</v>
@@ -9743,7 +9716,7 @@
         <v>138</v>
       </c>
       <c r="W37" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X37" s="56" t="s">
         <v>21</v>
@@ -9775,20 +9748,20 @@
         <v>24</v>
       </c>
       <c r="I38" s="56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J38" s="57">
         <v>40000</v>
       </c>
       <c r="K38" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L38" s="56"/>
       <c r="M38" s="56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N38" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O38" s="56">
         <v>80</v>
@@ -9815,7 +9788,7 @@
         <v>138</v>
       </c>
       <c r="W38" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X38" s="56" t="s">
         <v>21</v>
@@ -9847,20 +9820,20 @@
         <v>24</v>
       </c>
       <c r="I39" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J39" s="57">
         <v>40000</v>
       </c>
       <c r="K39" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L39" s="56"/>
       <c r="M39" s="56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N39" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O39" s="56">
         <v>80</v>
@@ -9887,7 +9860,7 @@
         <v>138</v>
       </c>
       <c r="W39" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X39" s="56" t="s">
         <v>21</v>
@@ -9898,7 +9871,7 @@
         <v>46092</v>
       </c>
       <c r="B40" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C40" s="44" t="s">
         <v>47</v>
@@ -9919,20 +9892,20 @@
         <v>17</v>
       </c>
       <c r="I40" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J40" s="57">
         <v>49900</v>
       </c>
       <c r="K40" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L40" s="56"/>
       <c r="M40" s="56" t="s">
         <v>138</v>
       </c>
       <c r="N40" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O40" s="56">
         <v>60</v>
@@ -9959,7 +9932,7 @@
         <v>138</v>
       </c>
       <c r="W40" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X40" s="56" t="s">
         <v>21</v>
@@ -9970,7 +9943,7 @@
         <v>46092</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="44" t="s">
         <v>47</v>
@@ -9991,20 +9964,20 @@
         <v>24</v>
       </c>
       <c r="I41" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J41" s="57">
         <v>79900</v>
       </c>
       <c r="K41" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N41" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O41" s="56">
         <v>80</v>
@@ -10031,7 +10004,7 @@
         <v>138</v>
       </c>
       <c r="W41" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X41" s="56" t="s">
         <v>21</v>
@@ -10042,7 +10015,7 @@
         <v>46092</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="44" t="s">
         <v>47</v>
@@ -10063,20 +10036,20 @@
         <v>17</v>
       </c>
       <c r="I42" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J42" s="57">
         <v>31000</v>
       </c>
       <c r="K42" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L42" s="56"/>
       <c r="M42" s="56" t="s">
         <v>138</v>
       </c>
       <c r="N42" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O42" s="56">
         <v>80</v>
@@ -10103,7 +10076,7 @@
         <v>138</v>
       </c>
       <c r="W42" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X42" s="56" t="s">
         <v>21</v>
@@ -10114,7 +10087,7 @@
         <v>46091</v>
       </c>
       <c r="B43" s="47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C43" s="44" t="s">
         <v>47</v>
@@ -10139,26 +10112,26 @@
         <v>84000</v>
       </c>
       <c r="K43" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="L43" s="56" t="s">
         <v>170</v>
-      </c>
-      <c r="L43" s="56" t="s">
-        <v>171</v>
       </c>
       <c r="M43" s="56">
         <v>200</v>
       </c>
       <c r="N43" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O43" s="56">
         <v>120</v>
       </c>
       <c r="P43" s="56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q43" s="58"/>
       <c r="R43" s="58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S43" s="58">
         <v>50000</v>
@@ -10169,10 +10142,10 @@
       </c>
       <c r="V43" s="56"/>
       <c r="W43" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="X43" s="56" t="s">
         <v>175</v>
-      </c>
-      <c r="X43" s="56" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10180,7 +10153,7 @@
         <v>46091</v>
       </c>
       <c r="B44" s="47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C44" s="44" t="s">
         <v>43</v>
@@ -10205,16 +10178,16 @@
         <v>84000</v>
       </c>
       <c r="K44" s="56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L44" s="56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M44" s="56">
         <v>400</v>
       </c>
       <c r="N44" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O44" s="56">
         <v>109</v>
@@ -10232,13 +10205,13 @@
         <v>2</v>
       </c>
       <c r="U44" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="V44" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="V44" s="56" t="s">
+      <c r="W44" s="56" t="s">
         <v>179</v>
-      </c>
-      <c r="W44" s="56" t="s">
-        <v>180</v>
       </c>
       <c r="X44" s="56" t="s">
         <v>21</v>
@@ -10249,7 +10222,7 @@
         <v>46091</v>
       </c>
       <c r="B45" s="47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C45" s="44" t="s">
         <v>43</v>
@@ -10274,16 +10247,16 @@
         <v>73000</v>
       </c>
       <c r="K45" s="56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L45" s="56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M45" s="56">
         <v>200</v>
       </c>
       <c r="N45" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O45" s="56">
         <v>109</v>
@@ -10302,16 +10275,16 @@
         <v>2</v>
       </c>
       <c r="U45" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="V45" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="V45" s="56" t="s">
+      <c r="W45" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="W45" s="56" t="s">
-        <v>180</v>
-      </c>
       <c r="X45" s="56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10319,7 +10292,7 @@
         <v>46092</v>
       </c>
       <c r="B46" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C46" s="44" t="s">
         <v>22</v>
@@ -10346,10 +10319,10 @@
         <v>89900</v>
       </c>
       <c r="K46" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="L46" s="56" t="s">
         <v>182</v>
-      </c>
-      <c r="L46" s="56" t="s">
-        <v>183</v>
       </c>
       <c r="M46" s="56" t="s">
         <v>137</v>
@@ -10391,7 +10364,7 @@
         <v>46092</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C47" s="44" t="s">
         <v>22</v>
@@ -10418,19 +10391,19 @@
         <v>109900</v>
       </c>
       <c r="K47" s="56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L47" s="56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M47" s="56" t="s">
         <v>137</v>
       </c>
       <c r="N47" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="O47" s="56" t="s">
         <v>185</v>
-      </c>
-      <c r="O47" s="56" t="s">
-        <v>186</v>
       </c>
       <c r="P47" s="56">
         <v>2</v>
@@ -10463,7 +10436,7 @@
         <v>46091</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>30</v>
@@ -10486,8 +10459,8 @@
       <c r="I48" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="J48" s="57" t="s">
-        <v>188</v>
+      <c r="J48" s="57">
+        <v>119900</v>
       </c>
       <c r="K48" s="56" t="s">
         <v>145</v>
@@ -10529,7 +10502,7 @@
         <v>46091</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>30</v>
@@ -10552,8 +10525,8 @@
       <c r="I49" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="J49" s="57" t="s">
-        <v>151</v>
+      <c r="J49" s="57">
+        <v>89900</v>
       </c>
       <c r="K49" s="56" t="s">
         <v>145</v>
@@ -10562,7 +10535,7 @@
         <v>102</v>
       </c>
       <c r="M49" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N49" s="56" t="s">
         <v>138</v>
@@ -10582,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V49" s="56" t="s">
         <v>139</v>
@@ -10597,7 +10570,7 @@
         <v>46091</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>30</v>
@@ -10618,10 +10591,10 @@
         <v>24</v>
       </c>
       <c r="I50" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="J50" s="57" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="J50" s="57">
+        <v>63700</v>
       </c>
       <c r="K50" s="56" t="s">
         <v>145</v>
@@ -10630,10 +10603,10 @@
         <v>102</v>
       </c>
       <c r="M50" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N50" s="56" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O50" s="56" t="s">
         <v>149</v>
@@ -10657,7 +10630,7 @@
         <v>46091</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C51" s="44" t="s">
         <v>30</v>
@@ -10678,25 +10651,25 @@
         <v>24</v>
       </c>
       <c r="I51" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="J51" s="57" t="s">
-        <v>193</v>
+        <v>187</v>
+      </c>
+      <c r="J51" s="57">
+        <v>86436</v>
       </c>
       <c r="K51" s="56" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L51" s="56" t="s">
         <v>102</v>
       </c>
       <c r="M51" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N51" s="56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O51" s="56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P51" s="56">
         <v>1</v>
@@ -10717,7 +10690,7 @@
         <v>46091</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C52" s="44" t="s">
         <v>14</v>
@@ -10738,19 +10711,19 @@
         <v>17</v>
       </c>
       <c r="I52" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J52" s="57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K52" s="56" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L52" s="56" t="s">
         <v>102</v>
       </c>
       <c r="M52" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N52" s="56" t="s">
         <v>138</v>
@@ -10770,7 +10743,7 @@
       <c r="U52" s="58"/>
       <c r="V52" s="56"/>
       <c r="W52" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X52" s="56" t="s">
         <v>21</v>
@@ -10781,7 +10754,7 @@
         <v>46091</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>14</v>
@@ -10802,25 +10775,25 @@
         <v>24</v>
       </c>
       <c r="I53" s="56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J53" s="57" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K53" s="56" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L53" s="56" t="s">
         <v>102</v>
       </c>
       <c r="M53" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N53" s="56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O53" s="56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P53" s="56">
         <v>1</v>
@@ -10841,7 +10814,7 @@
         <v>46091</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>14</v>
@@ -10862,25 +10835,25 @@
         <v>24</v>
       </c>
       <c r="I54" s="56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J54" s="57" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K54" s="56" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L54" s="56" t="s">
         <v>102</v>
       </c>
       <c r="M54" s="56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N54" s="56" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O54" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P54" s="56" t="s">
         <v>138</v>
@@ -10894,7 +10867,7 @@
       <c r="U54" s="58"/>
       <c r="V54" s="56"/>
       <c r="W54" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X54" s="56" t="s">
         <v>21</v>
@@ -10905,7 +10878,7 @@
         <v>46091</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C55" s="44" t="s">
         <v>14</v>
@@ -10929,10 +10902,10 @@
         <v>134</v>
       </c>
       <c r="J55" s="77" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K55" s="77" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L55" s="77" t="s">
         <v>102</v>
@@ -10963,7 +10936,7 @@
         <v>46091</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C56" s="44" t="s">
         <v>14</v>
@@ -10987,10 +10960,10 @@
         <v>134</v>
       </c>
       <c r="J56" s="77" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K56" s="77" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L56" s="77" t="s">
         <v>102</v>
@@ -11010,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="U56" s="77" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="V56" s="77" t="s">
         <v>139</v>
@@ -11025,7 +10998,7 @@
         <v>46091</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C57" s="44" t="s">
         <v>14</v>
@@ -11049,10 +11022,10 @@
         <v>134</v>
       </c>
       <c r="J57" s="77" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K57" s="77" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L57" s="77" t="s">
         <v>102</v>
@@ -11061,7 +11034,7 @@
         <v>137</v>
       </c>
       <c r="N57" s="77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O57" s="76"/>
       <c r="P57" s="76">
@@ -11085,7 +11058,7 @@
         <v>46091</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C58" s="44" t="s">
         <v>14</v>
@@ -11109,10 +11082,10 @@
         <v>134</v>
       </c>
       <c r="J58" s="77" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K58" s="77" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L58" s="77" t="s">
         <v>102</v>
@@ -11121,7 +11094,7 @@
         <v>137</v>
       </c>
       <c r="N58" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O58" s="78"/>
       <c r="P58" s="78">
@@ -11134,7 +11107,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="50" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="V58" s="50" t="s">
         <v>139</v>
@@ -11149,7 +11122,7 @@
         <v>46091</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C59" s="44" t="s">
         <v>14</v>
@@ -11170,49 +11143,49 @@
         <v>17</v>
       </c>
       <c r="I59" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="J59" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="K59" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="L59" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="J59" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="K59" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="L59" s="77" t="s">
-        <v>217</v>
-      </c>
       <c r="M59" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W59" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X59" s="77" t="s">
         <v>21</v>
@@ -11223,7 +11196,7 @@
         <v>46091</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C60" s="44" t="s">
         <v>14</v>
@@ -11244,49 +11217,49 @@
         <v>24</v>
       </c>
       <c r="I60" s="77" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J60" s="77" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K60" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="L60" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="M60" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="L60" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="M60" s="77" t="s">
-        <v>219</v>
-      </c>
       <c r="N60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W60" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X60" s="77" t="s">
         <v>21</v>
@@ -11297,7 +11270,7 @@
         <v>46091</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C61" s="44" t="s">
         <v>14</v>
@@ -11318,49 +11291,49 @@
         <v>17</v>
       </c>
       <c r="I61" s="77" t="s">
+        <v>211</v>
+      </c>
+      <c r="J61" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="K61" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="L61" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="J61" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="K61" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="L61" s="77" t="s">
-        <v>217</v>
-      </c>
       <c r="M61" s="77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W61" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X61" s="77" t="s">
         <v>21</v>
@@ -11371,7 +11344,7 @@
         <v>46091</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C62" s="44" t="s">
         <v>14</v>
@@ -11392,49 +11365,49 @@
         <v>17</v>
       </c>
       <c r="I62" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="J62" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="K62" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="L62" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="J62" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="K62" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="L62" s="77" t="s">
-        <v>217</v>
-      </c>
       <c r="M62" s="77" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V62" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W62" s="50" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X62" s="77" t="s">
         <v>21</v>
@@ -11445,7 +11418,7 @@
         <v>46092</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C63" s="44" t="s">
         <v>14</v>
@@ -11472,10 +11445,10 @@
         <v>89900</v>
       </c>
       <c r="K63" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="L63" s="56" t="s">
         <v>182</v>
-      </c>
-      <c r="L63" s="56" t="s">
-        <v>183</v>
       </c>
       <c r="M63" s="56" t="s">
         <v>137</v>
@@ -11517,7 +11490,7 @@
         <v>46092</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C64" s="44" t="s">
         <v>14</v>
@@ -11544,19 +11517,19 @@
         <v>109900</v>
       </c>
       <c r="K64" s="56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L64" s="56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M64" s="56" t="s">
         <v>137</v>
       </c>
       <c r="N64" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="O64" s="56" t="s">
         <v>185</v>
-      </c>
-      <c r="O64" s="56" t="s">
-        <v>186</v>
       </c>
       <c r="P64" s="56">
         <v>2</v>
@@ -11589,7 +11562,7 @@
         <v>46092</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C65" s="44" t="s">
         <v>14</v>
@@ -11612,8 +11585,8 @@
       <c r="I65" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="J65" s="57" t="s">
-        <v>151</v>
+      <c r="J65" s="57">
+        <v>89900</v>
       </c>
       <c r="K65" s="56" t="s">
         <v>145</v>
@@ -11622,7 +11595,7 @@
         <v>102</v>
       </c>
       <c r="M65" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N65" s="56" t="s">
         <v>138</v>
@@ -11642,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="U65" s="58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V65" s="56" t="s">
         <v>139</v>
@@ -11657,7 +11630,7 @@
         <v>46092</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C66" s="44" t="s">
         <v>14</v>
@@ -11678,10 +11651,10 @@
         <v>24</v>
       </c>
       <c r="I66" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="J66" s="57" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="J66" s="57">
+        <v>63700</v>
       </c>
       <c r="K66" s="56" t="s">
         <v>145</v>
@@ -11690,10 +11663,10 @@
         <v>102</v>
       </c>
       <c r="M66" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N66" s="56" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O66" s="56" t="s">
         <v>149</v>
@@ -11717,7 +11690,7 @@
         <v>46092</v>
       </c>
       <c r="B67" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C67" s="44" t="s">
         <v>14</v>
@@ -11740,8 +11713,8 @@
       <c r="I67" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="J67" s="57" t="s">
-        <v>188</v>
+      <c r="J67" s="57">
+        <v>119900</v>
       </c>
       <c r="K67" s="56" t="s">
         <v>145</v>
@@ -11783,7 +11756,7 @@
         <v>46092</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C68" s="44" t="s">
         <v>14</v>
@@ -11804,19 +11777,19 @@
         <v>17</v>
       </c>
       <c r="I68" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="J68" s="52" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="J68" s="52">
+        <v>49900</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L68" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M68" s="51" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N68" s="51" t="s">
         <v>138</v>
@@ -11836,7 +11809,7 @@
       <c r="U68" s="53"/>
       <c r="V68" s="51"/>
       <c r="W68" s="51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X68" s="51" t="s">
         <v>21</v>
@@ -11847,7 +11820,7 @@
         <v>46092</v>
       </c>
       <c r="B69" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C69" s="44" t="s">
         <v>14</v>
@@ -11868,25 +11841,25 @@
         <v>24</v>
       </c>
       <c r="I69" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="J69" s="52" t="s">
-        <v>193</v>
+        <v>187</v>
+      </c>
+      <c r="J69" s="52">
+        <v>86436</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L69" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M69" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N69" s="51" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O69" s="51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P69" s="51">
         <v>1</v>
@@ -11907,7 +11880,7 @@
         <v>46092</v>
       </c>
       <c r="B70" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C70" s="44" t="s">
         <v>14</v>
@@ -11928,19 +11901,19 @@
         <v>17</v>
       </c>
       <c r="I70" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="J70" s="52" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="J70" s="52">
+        <v>49900</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L70" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M70" s="51" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N70" s="51" t="s">
         <v>138</v>
@@ -11960,7 +11933,7 @@
       <c r="U70" s="53"/>
       <c r="V70" s="51"/>
       <c r="W70" s="51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="X70" s="51" t="s">
         <v>21</v>
@@ -11971,7 +11944,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C71" s="44" t="s">
         <v>14</v>
@@ -11992,25 +11965,25 @@
         <v>24</v>
       </c>
       <c r="I71" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="J71" s="52" t="s">
-        <v>193</v>
+        <v>187</v>
+      </c>
+      <c r="J71" s="52">
+        <v>86436</v>
       </c>
       <c r="K71" s="51" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L71" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M71" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N71" s="51" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O71" s="51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P71" s="51">
         <v>1</v>
@@ -12031,7 +12004,7 @@
         <v>46092</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C72" s="44" t="s">
         <v>14</v>
@@ -12052,49 +12025,49 @@
         <v>17</v>
       </c>
       <c r="I72" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="J72" s="50">
+        <v>54900</v>
+      </c>
+      <c r="K72" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="L72" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="J72" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="K72" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="L72" s="50" t="s">
-        <v>217</v>
-      </c>
       <c r="M72" s="50" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V72" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W72" s="50" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X72" s="50" t="s">
         <v>21</v>
@@ -12105,7 +12078,7 @@
         <v>46092</v>
       </c>
       <c r="B73" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C73" s="44" t="s">
         <v>14</v>
@@ -12126,49 +12099,49 @@
         <v>17</v>
       </c>
       <c r="I73" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="J73" s="50">
+        <v>54900</v>
+      </c>
+      <c r="K73" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="L73" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="J73" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="K73" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="L73" s="50" t="s">
-        <v>217</v>
-      </c>
       <c r="M73" s="50" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V73" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W73" s="50" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X73" s="50" t="s">
         <v>21</v>
@@ -12179,7 +12152,7 @@
         <v>46092</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C74" s="44" t="s">
         <v>14</v>
@@ -12200,49 +12173,49 @@
         <v>17</v>
       </c>
       <c r="I74" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="J74" s="50">
+        <v>54900</v>
+      </c>
+      <c r="K74" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="L74" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="J74" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="K74" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="L74" s="50" t="s">
-        <v>217</v>
-      </c>
       <c r="M74" s="50" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="T74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V74" s="78" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W74" s="50" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X74" s="50" t="s">
         <v>21</v>
@@ -12253,7 +12226,7 @@
         <v>46092</v>
       </c>
       <c r="B75" s="50" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C75" s="44" t="s">
         <v>14</v>
@@ -12278,10 +12251,10 @@
         <v>94990</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L75" s="51" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M75" s="51">
         <v>949990</v>
@@ -12311,7 +12284,7 @@
         <v>138</v>
       </c>
       <c r="V75" s="51" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="W75" s="51"/>
       <c r="X75" s="51"/>
@@ -12321,7 +12294,7 @@
         <v>46092</v>
       </c>
       <c r="B76" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C76" s="44" t="s">
         <v>47</v>
@@ -12342,7 +12315,7 @@
         <v>17</v>
       </c>
       <c r="I76" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J76" s="57">
         <v>30000</v>
@@ -12353,7 +12326,7 @@
         <v>138</v>
       </c>
       <c r="N76" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O76" s="56">
         <v>80</v>
@@ -12380,7 +12353,7 @@
         <v>138</v>
       </c>
       <c r="W76" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X76" s="56" t="s">
         <v>21</v>
@@ -12412,19 +12385,19 @@
         <v>17</v>
       </c>
       <c r="I77" s="51" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J77" s="52">
         <v>75000</v>
       </c>
       <c r="K77" s="51" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L77" s="51" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M77" s="51" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N77" s="51" t="s">
         <v>138</v>
@@ -12454,7 +12427,7 @@
         <v>138</v>
       </c>
       <c r="W77" s="51" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="X77" s="51" t="s">
         <v>21</v>
@@ -12486,19 +12459,19 @@
         <v>17</v>
       </c>
       <c r="I78" s="51" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J78" s="52">
         <v>120000</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L78" s="51" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M78" s="51" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N78" s="51" t="s">
         <v>138</v>
@@ -12510,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="53" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="R78" s="53" t="s">
         <v>138</v>
@@ -12528,7 +12501,7 @@
         <v>138</v>
       </c>
       <c r="W78" s="51" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="X78" s="51" t="s">
         <v>21</v>
@@ -12539,7 +12512,7 @@
         <v>46092</v>
       </c>
       <c r="B79" s="50" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C79" s="44" t="s">
         <v>14</v>
@@ -12560,19 +12533,19 @@
         <v>17</v>
       </c>
       <c r="I79" s="51" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J79" s="52">
         <v>84900</v>
       </c>
       <c r="K79" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L79" s="51" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M79" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N79" s="51" t="s">
         <v>138</v>
@@ -12632,20 +12605,20 @@
         <v>17</v>
       </c>
       <c r="I80" s="51" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J80" s="52">
         <v>24000</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L80" s="51"/>
       <c r="M80" s="51" t="s">
         <v>138</v>
       </c>
       <c r="N80" s="51" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O80" s="51">
         <v>100</v>
@@ -12672,7 +12645,7 @@
         <v>138</v>
       </c>
       <c r="W80" s="51" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="X80" s="51" t="s">
         <v>21</v>
@@ -12704,22 +12677,22 @@
         <v>24</v>
       </c>
       <c r="I81" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J81" s="52">
         <v>60000</v>
       </c>
       <c r="K81" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="L81" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="M81" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="L81" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="M81" s="51" t="s">
-        <v>245</v>
-      </c>
       <c r="N81" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O81" s="51">
         <v>80</v>
@@ -12746,7 +12719,7 @@
         <v>138</v>
       </c>
       <c r="W81" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X81" s="51" t="s">
         <v>21</v>
@@ -12778,22 +12751,22 @@
         <v>24</v>
       </c>
       <c r="I82" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J82" s="52">
         <v>75800</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L82" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M82" s="51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N82" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O82" s="51">
         <v>80</v>
@@ -12820,7 +12793,7 @@
         <v>138</v>
       </c>
       <c r="W82" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X82" s="51" t="s">
         <v>21</v>
@@ -12852,22 +12825,22 @@
         <v>24</v>
       </c>
       <c r="I83" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J83" s="52">
         <v>97800</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L83" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M83" s="51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N83" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O83" s="51">
         <v>80</v>
@@ -12894,7 +12867,7 @@
         <v>138</v>
       </c>
       <c r="W83" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X83" s="51" t="s">
         <v>21</v>
@@ -12905,7 +12878,7 @@
         <v>46092</v>
       </c>
       <c r="B84" s="50" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C84" s="44" t="s">
         <v>14</v>
@@ -12961,22 +12934,22 @@
         <v>24</v>
       </c>
       <c r="I85" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J85" s="52">
         <v>60000</v>
       </c>
       <c r="K85" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="L85" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="M85" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="L85" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="M85" s="51" t="s">
-        <v>245</v>
-      </c>
       <c r="N85" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O85" s="51">
         <v>80</v>
@@ -13003,7 +12976,7 @@
         <v>138</v>
       </c>
       <c r="W85" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X85" s="51" t="s">
         <v>21</v>
@@ -13035,22 +13008,22 @@
         <v>24</v>
       </c>
       <c r="I86" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J86" s="52">
         <v>75800</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L86" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M86" s="51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N86" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O86" s="51">
         <v>80</v>
@@ -13077,7 +13050,7 @@
         <v>138</v>
       </c>
       <c r="W86" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X86" s="51" t="s">
         <v>21</v>
@@ -13109,22 +13082,22 @@
         <v>24</v>
       </c>
       <c r="I87" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J87" s="52">
         <v>97800</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L87" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M87" s="51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N87" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O87" s="51">
         <v>80</v>
@@ -13151,7 +13124,7 @@
         <v>138</v>
       </c>
       <c r="W87" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X87" s="51" t="s">
         <v>21</v>
@@ -13183,23 +13156,23 @@
         <v>17</v>
       </c>
       <c r="I88" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J88" s="52">
         <v>78000</v>
       </c>
       <c r="K88" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="L88" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="M88" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="L88" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="M88" s="51" t="s">
+      <c r="N88" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="N88" s="51" t="s">
-        <v>248</v>
-      </c>
       <c r="O88" s="51" t="s">
         <v>138</v>
       </c>
@@ -13225,7 +13198,7 @@
         <v>138</v>
       </c>
       <c r="W88" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X88" s="51" t="s">
         <v>21</v>
@@ -13257,22 +13230,22 @@
         <v>17</v>
       </c>
       <c r="I89" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J89" s="52">
         <v>99000</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L89" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M89" s="51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N89" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O89" s="51" t="s">
         <v>138</v>
@@ -13299,7 +13272,7 @@
         <v>138</v>
       </c>
       <c r="W89" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X89" s="51" t="s">
         <v>21</v>
@@ -13331,22 +13304,22 @@
         <v>17</v>
       </c>
       <c r="I90" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J90" s="52">
         <v>119000</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L90" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M90" s="51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N90" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O90" s="51" t="s">
         <v>138</v>
@@ -13373,7 +13346,7 @@
         <v>138</v>
       </c>
       <c r="W90" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X90" s="51" t="s">
         <v>21</v>
@@ -13405,22 +13378,22 @@
         <v>17</v>
       </c>
       <c r="I91" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J91" s="52">
         <v>61000</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L91" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M91" s="51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N91" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O91" s="51" t="s">
         <v>138</v>
@@ -13447,7 +13420,7 @@
         <v>138</v>
       </c>
       <c r="W91" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X91" s="51" t="s">
         <v>21</v>
@@ -13479,23 +13452,23 @@
         <v>17</v>
       </c>
       <c r="I92" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J92" s="52">
         <v>78000</v>
       </c>
       <c r="K92" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="L92" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="M92" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="L92" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="M92" s="51" t="s">
+      <c r="N92" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="N92" s="51" t="s">
-        <v>248</v>
-      </c>
       <c r="O92" s="51" t="s">
         <v>138</v>
       </c>
@@ -13521,7 +13494,7 @@
         <v>138</v>
       </c>
       <c r="W92" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X92" s="51" t="s">
         <v>21</v>
@@ -13553,22 +13526,22 @@
         <v>17</v>
       </c>
       <c r="I93" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J93" s="52">
         <v>99000</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L93" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M93" s="51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N93" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O93" s="51" t="s">
         <v>138</v>
@@ -13595,7 +13568,7 @@
         <v>138</v>
       </c>
       <c r="W93" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X93" s="51" t="s">
         <v>21</v>
@@ -13627,22 +13600,22 @@
         <v>17</v>
       </c>
       <c r="I94" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J94" s="52">
         <v>119000</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L94" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M94" s="51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N94" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O94" s="51" t="s">
         <v>138</v>
@@ -13669,7 +13642,7 @@
         <v>138</v>
       </c>
       <c r="W94" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X94" s="51" t="s">
         <v>21</v>
@@ -13701,22 +13674,22 @@
         <v>17</v>
       </c>
       <c r="I95" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J95" s="52">
         <v>61000</v>
       </c>
       <c r="K95" s="51" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L95" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M95" s="51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N95" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O95" s="51" t="s">
         <v>138</v>
@@ -13743,7 +13716,7 @@
         <v>138</v>
       </c>
       <c r="W95" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X95" s="51" t="s">
         <v>21</v>
@@ -13754,7 +13727,7 @@
         <v>46092</v>
       </c>
       <c r="B96" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C96" s="44" t="s">
         <v>14</v>
@@ -13775,22 +13748,22 @@
         <v>24</v>
       </c>
       <c r="I96" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J96" s="61">
         <v>65.567999999999998</v>
       </c>
       <c r="K96" s="51" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L96" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M96" s="56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N96" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O96" s="56">
         <v>40</v>
@@ -13817,7 +13790,7 @@
         <v>138</v>
       </c>
       <c r="W96" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X96" s="51" t="s">
         <v>21</v>
@@ -13828,7 +13801,7 @@
         <v>46092</v>
       </c>
       <c r="B97" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C97" s="44" t="s">
         <v>14</v>
@@ -13849,20 +13822,20 @@
         <v>24</v>
       </c>
       <c r="I97" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J97" s="57"/>
       <c r="K97" s="51" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L97" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M97" s="56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N97" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O97" s="56">
         <v>40</v>
@@ -13889,7 +13862,7 @@
         <v>138</v>
       </c>
       <c r="W97" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X97" s="51" t="s">
         <v>21</v>
@@ -13921,7 +13894,7 @@
         <v>24</v>
       </c>
       <c r="I98" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J98" s="57">
         <v>109900</v>
@@ -13933,10 +13906,10 @@
         <v>138</v>
       </c>
       <c r="M98" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N98" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O98" s="56" t="s">
         <v>138</v>
@@ -13963,7 +13936,7 @@
         <v>138</v>
       </c>
       <c r="W98" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X98" s="56" t="s">
         <v>21</v>
@@ -13995,7 +13968,7 @@
         <v>24</v>
       </c>
       <c r="I99" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J99" s="57">
         <v>109900</v>
@@ -14007,11 +13980,11 @@
         <v>138</v>
       </c>
       <c r="M99" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="N99" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="N99" s="56" t="s">
-        <v>255</v>
-      </c>
       <c r="O99" s="56" t="s">
         <v>138</v>
       </c>
@@ -14037,7 +14010,7 @@
         <v>138</v>
       </c>
       <c r="W99" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X99" s="56" t="s">
         <v>21</v>
@@ -14069,7 +14042,7 @@
         <v>24</v>
       </c>
       <c r="I100" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J100" s="57">
         <v>109900</v>
@@ -14081,10 +14054,10 @@
         <v>138</v>
       </c>
       <c r="M100" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N100" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O100" s="56" t="s">
         <v>138</v>
@@ -14111,7 +14084,7 @@
         <v>138</v>
       </c>
       <c r="W100" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X100" s="56" t="s">
         <v>21</v>
@@ -14122,7 +14095,7 @@
         <v>46092</v>
       </c>
       <c r="B101" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C101" s="44" t="s">
         <v>14</v>
@@ -14143,7 +14116,7 @@
         <v>24</v>
       </c>
       <c r="I101" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J101" s="61">
         <v>84.850999999999999</v>
@@ -14155,10 +14128,10 @@
         <v>138</v>
       </c>
       <c r="M101" s="56" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N101" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O101" s="56">
         <v>40</v>
@@ -14185,7 +14158,7 @@
         <v>138</v>
       </c>
       <c r="W101" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X101" s="56" t="s">
         <v>21</v>
@@ -14196,7 +14169,7 @@
         <v>46092</v>
       </c>
       <c r="B102" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C102" s="44" t="s">
         <v>14</v>
@@ -14217,10 +14190,10 @@
         <v>24</v>
       </c>
       <c r="I102" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J102" s="61">
-        <v>109.17100000000001</v>
+        <v>109171</v>
       </c>
       <c r="K102" s="56" t="s">
         <v>138</v>
@@ -14229,10 +14202,10 @@
         <v>138</v>
       </c>
       <c r="M102" s="56" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N102" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O102" s="56">
         <v>40</v>
@@ -14259,7 +14232,7 @@
         <v>138</v>
       </c>
       <c r="W102" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X102" s="56" t="s">
         <v>21</v>
@@ -14291,7 +14264,7 @@
         <v>24</v>
       </c>
       <c r="I103" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J103" s="57">
         <v>99900</v>
@@ -14303,10 +14276,10 @@
         <v>138</v>
       </c>
       <c r="M103" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N103" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O103" s="56" t="s">
         <v>138</v>
@@ -14333,7 +14306,7 @@
         <v>138</v>
       </c>
       <c r="W103" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X103" s="56" t="s">
         <v>21</v>
@@ -14365,7 +14338,7 @@
         <v>24</v>
       </c>
       <c r="I104" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J104" s="57">
         <v>99900</v>
@@ -14377,11 +14350,11 @@
         <v>138</v>
       </c>
       <c r="M104" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="N104" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="N104" s="56" t="s">
-        <v>255</v>
-      </c>
       <c r="O104" s="56" t="s">
         <v>138</v>
       </c>
@@ -14407,7 +14380,7 @@
         <v>138</v>
       </c>
       <c r="W104" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X104" s="56" t="s">
         <v>21</v>
@@ -14439,7 +14412,7 @@
         <v>24</v>
       </c>
       <c r="I105" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J105" s="57">
         <v>99900</v>
@@ -14451,37 +14424,37 @@
         <v>138</v>
       </c>
       <c r="M105" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N105" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="O105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="P105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="R105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="S105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="T105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="U105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="V105" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="W105" s="56" t="s">
         <v>256</v>
-      </c>
-      <c r="O105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="P105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="R105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="S105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="T105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="U105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="V105" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="W105" s="56" t="s">
-        <v>259</v>
       </c>
       <c r="X105" s="56" t="s">
         <v>21</v>
@@ -14513,7 +14486,7 @@
         <v>24</v>
       </c>
       <c r="I106" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J106" s="57">
         <v>109900</v>
@@ -14525,10 +14498,10 @@
         <v>138</v>
       </c>
       <c r="M106" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N106" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O106" s="56" t="s">
         <v>138</v>
@@ -14555,7 +14528,7 @@
         <v>138</v>
       </c>
       <c r="W106" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X106" s="56" t="s">
         <v>21</v>
@@ -14587,7 +14560,7 @@
         <v>24</v>
       </c>
       <c r="I107" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J107" s="57">
         <v>109900</v>
@@ -14599,11 +14572,11 @@
         <v>138</v>
       </c>
       <c r="M107" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="N107" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="N107" s="56" t="s">
-        <v>255</v>
-      </c>
       <c r="O107" s="56" t="s">
         <v>138</v>
       </c>
@@ -14629,7 +14602,7 @@
         <v>138</v>
       </c>
       <c r="W107" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X107" s="56" t="s">
         <v>21</v>
@@ -14661,7 +14634,7 @@
         <v>24</v>
       </c>
       <c r="I108" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J108" s="57">
         <v>109900</v>
@@ -14673,10 +14646,10 @@
         <v>138</v>
       </c>
       <c r="M108" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N108" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O108" s="56" t="s">
         <v>138</v>
@@ -14703,7 +14676,7 @@
         <v>138</v>
       </c>
       <c r="W108" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X108" s="56" t="s">
         <v>21</v>
@@ -14735,7 +14708,7 @@
         <v>24</v>
       </c>
       <c r="I109" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J109" s="57">
         <v>99900</v>
@@ -14747,10 +14720,10 @@
         <v>138</v>
       </c>
       <c r="M109" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N109" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O109" s="56" t="s">
         <v>138</v>
@@ -14777,7 +14750,7 @@
         <v>138</v>
       </c>
       <c r="W109" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X109" s="56" t="s">
         <v>21</v>
@@ -14809,7 +14782,7 @@
         <v>24</v>
       </c>
       <c r="I110" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J110" s="57">
         <v>99900</v>
@@ -14821,11 +14794,11 @@
         <v>138</v>
       </c>
       <c r="M110" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="N110" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="N110" s="56" t="s">
-        <v>255</v>
-      </c>
       <c r="O110" s="56" t="s">
         <v>138</v>
       </c>
@@ -14851,7 +14824,7 @@
         <v>138</v>
       </c>
       <c r="W110" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X110" s="56" t="s">
         <v>21</v>
@@ -14883,7 +14856,7 @@
         <v>24</v>
       </c>
       <c r="I111" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J111" s="57">
         <v>99900</v>
@@ -14895,37 +14868,37 @@
         <v>138</v>
       </c>
       <c r="M111" s="56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N111" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="O111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="P111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="R111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="S111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="T111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="U111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="V111" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="W111" s="56" t="s">
         <v>256</v>
-      </c>
-      <c r="O111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="P111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="R111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="S111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="T111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="U111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="V111" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="W111" s="56" t="s">
-        <v>259</v>
       </c>
       <c r="X111" s="56" t="s">
         <v>21</v>
@@ -14936,7 +14909,7 @@
         <v>46092</v>
       </c>
       <c r="B112" s="47" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C112" s="44" t="s">
         <v>14</v>
@@ -14957,7 +14930,7 @@
         <v>32</v>
       </c>
       <c r="I112" s="56" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J112" s="57">
         <v>119900</v>
@@ -14969,10 +14942,10 @@
         <v>138</v>
       </c>
       <c r="M112" s="56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="O112" s="56">
         <v>156</v>
@@ -14993,7 +14966,7 @@
         <v>138</v>
       </c>
       <c r="U112" s="56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="V112" s="56" t="s">
         <v>138</v>
@@ -15010,7 +14983,7 @@
         <v>46092</v>
       </c>
       <c r="B113" s="47" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C113" s="44" t="s">
         <v>14</v>
@@ -15031,7 +15004,7 @@
         <v>38</v>
       </c>
       <c r="I113" s="56" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J113" s="57">
         <v>89900</v>
@@ -15043,7 +15016,7 @@
         <v>138</v>
       </c>
       <c r="M113" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N113" s="56" t="s">
         <v>138</v>
@@ -15067,7 +15040,7 @@
         <v>1</v>
       </c>
       <c r="U113" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="V113" s="56" t="s">
         <v>138</v>
@@ -15084,7 +15057,7 @@
         <v>46092</v>
       </c>
       <c r="B114" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C114" s="44" t="s">
         <v>37</v>
@@ -15105,49 +15078,49 @@
         <v>17</v>
       </c>
       <c r="I114" s="56" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J114" s="57">
         <v>63000</v>
       </c>
       <c r="K114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M114" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q114" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R114" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S114" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T114" s="58">
         <v>1</v>
       </c>
       <c r="U114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W114" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X114" s="56" t="s">
         <v>42</v>
@@ -15158,7 +15131,7 @@
         <v>46092</v>
       </c>
       <c r="B115" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C115" s="44" t="s">
         <v>37</v>
@@ -15179,49 +15152,49 @@
         <v>17</v>
       </c>
       <c r="I115" s="56" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J115" s="57">
         <v>100000</v>
       </c>
       <c r="K115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M115" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q115" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R115" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S115" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T115" s="58">
         <v>1</v>
       </c>
       <c r="U115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V115" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W115" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X115" s="56" t="s">
         <v>42</v>
@@ -15232,7 +15205,7 @@
         <v>46092</v>
       </c>
       <c r="B116" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C116" s="44" t="s">
         <v>37</v>
@@ -15253,49 +15226,49 @@
         <v>17</v>
       </c>
       <c r="I116" s="56" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J116" s="57">
         <v>75000</v>
       </c>
       <c r="K116" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L116" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M116" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O116" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P116" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q116" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R116" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S116" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T116" s="58">
         <v>1</v>
       </c>
       <c r="U116" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="V116" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="W116" s="56" t="s">
         <v>269</v>
-      </c>
-      <c r="V116" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="W116" s="56" t="s">
-        <v>272</v>
       </c>
       <c r="X116" s="56" t="s">
         <v>42</v>
@@ -15306,7 +15279,7 @@
         <v>46092</v>
       </c>
       <c r="B117" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C117" s="44" t="s">
         <v>59</v>
@@ -15327,22 +15300,22 @@
         <v>24</v>
       </c>
       <c r="I117" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J117" s="57">
         <v>99000</v>
       </c>
       <c r="K117" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L117" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M117" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O117" s="56">
         <v>80</v>
@@ -15351,25 +15324,25 @@
         <v>1</v>
       </c>
       <c r="Q117" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R117" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S117" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T117" s="58">
         <v>1</v>
       </c>
       <c r="U117" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V117" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W117" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X117" s="56" t="s">
         <v>42</v>
@@ -15380,7 +15353,7 @@
         <v>46092</v>
       </c>
       <c r="B118" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C118" s="44" t="s">
         <v>59</v>
@@ -15401,49 +15374,49 @@
         <v>17</v>
       </c>
       <c r="I118" s="56" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J118" s="57">
         <v>65000</v>
       </c>
       <c r="K118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M118" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q118" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R118" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S118" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T118" s="58">
         <v>1</v>
       </c>
       <c r="U118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W118" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="X118" s="56" t="s">
         <v>21</v>
@@ -15454,7 +15427,7 @@
         <v>46092</v>
       </c>
       <c r="B119" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C119" s="44" t="s">
         <v>47</v>
@@ -15477,8 +15450,8 @@
       <c r="I119" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="J119" s="57" t="s">
-        <v>277</v>
+      <c r="J119" s="57">
+        <v>48000</v>
       </c>
       <c r="K119" s="56" t="s">
         <v>138</v>
@@ -15487,19 +15460,19 @@
         <v>138</v>
       </c>
       <c r="M119" s="56" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O119" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P119" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q119" s="58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R119" s="58" t="s">
         <v>25</v>
@@ -15511,13 +15484,13 @@
         <v>138</v>
       </c>
       <c r="U119" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V119" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W119" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X119" s="56" t="s">
         <v>42</v>
@@ -15528,7 +15501,7 @@
         <v>46092</v>
       </c>
       <c r="B120" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C120" s="44" t="s">
         <v>47</v>
@@ -15549,10 +15522,10 @@
         <v>24</v>
       </c>
       <c r="I120" s="56" t="s">
-        <v>279</v>
-      </c>
-      <c r="J120" s="57" t="s">
-        <v>280</v>
+        <v>275</v>
+      </c>
+      <c r="J120" s="57">
+        <v>69000</v>
       </c>
       <c r="K120" s="56" t="s">
         <v>138</v>
@@ -15561,10 +15534,10 @@
         <v>138</v>
       </c>
       <c r="M120" s="56" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O120" s="56">
         <v>110</v>
@@ -15591,7 +15564,7 @@
         <v>138</v>
       </c>
       <c r="W120" s="56" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="X120" s="56" t="s">
         <v>42</v>
@@ -15602,7 +15575,7 @@
         <v>46092</v>
       </c>
       <c r="B121" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C121" s="44" t="s">
         <v>47</v>
@@ -15623,22 +15596,22 @@
         <v>24</v>
       </c>
       <c r="I121" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="J121" s="57">
+        <v>45000</v>
+      </c>
+      <c r="K121" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="L121" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="M121" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="N121" s="56" t="s">
         <v>279</v>
-      </c>
-      <c r="J121" s="57" t="s">
-        <v>283</v>
-      </c>
-      <c r="K121" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="L121" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="M121" s="56" t="s">
-        <v>284</v>
-      </c>
-      <c r="N121" s="56" t="s">
-        <v>285</v>
       </c>
       <c r="O121" s="56">
         <v>62</v>
@@ -15662,10 +15635,10 @@
         <v>138</v>
       </c>
       <c r="V121" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W121" s="56" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="X121" s="56" t="s">
         <v>42</v>
@@ -15676,7 +15649,7 @@
         <v>46092</v>
       </c>
       <c r="B122" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C122" s="44" t="s">
         <v>47</v>
@@ -15697,10 +15670,10 @@
         <v>17</v>
       </c>
       <c r="I122" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="J122" s="57" t="s">
-        <v>287</v>
+        <v>272</v>
+      </c>
+      <c r="J122" s="57">
+        <v>56000</v>
       </c>
       <c r="K122" s="56" t="s">
         <v>138</v>
@@ -15709,10 +15682,10 @@
         <v>138</v>
       </c>
       <c r="M122" s="56" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="O122" s="56" t="s">
         <v>138</v>
@@ -15739,7 +15712,7 @@
         <v>138</v>
       </c>
       <c r="W122" s="56" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="X122" s="56" t="s">
         <v>42</v>
@@ -17208,7 +17181,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -17234,46 +17207,46 @@
         <v>85</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="40" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>97</v>
       </c>
       <c r="O2" s="41" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -17281,7 +17254,7 @@
         <v>46087</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="2" t="s">
@@ -17291,34 +17264,34 @@
         <v>39900</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G3" s="26">
         <v>12</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N3" s="26" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P3" s="30"/>
     </row>
@@ -17327,7 +17300,7 @@
         <v>46087</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="27" t="s">
@@ -17337,7 +17310,7 @@
         <v>53900</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="G4" s="15">
         <v>2</v>
@@ -17346,25 +17319,25 @@
         <v>60</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P4" s="30"/>
     </row>
@@ -17373,7 +17346,7 @@
         <v>46087</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="27" t="s">
@@ -17385,28 +17358,28 @@
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P5" s="30"/>
     </row>
@@ -17415,7 +17388,7 @@
         <v>46087</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="27" t="s">
@@ -17425,7 +17398,7 @@
         <v>45990</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="G6" s="15">
         <v>1</v>
@@ -17434,25 +17407,25 @@
         <v>50</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J6" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>309</v>
-      </c>
       <c r="M6" s="15" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P6" s="30"/>
     </row>
@@ -17461,7 +17434,7 @@
         <v>46087</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="27" t="s">
@@ -17471,7 +17444,7 @@
         <v>52990</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G7" s="15">
         <v>1</v>
@@ -17480,21 +17453,21 @@
         <v>65</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P7" s="30"/>
     </row>
@@ -17503,7 +17476,7 @@
         <v>46087</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="27" t="s">
@@ -17513,30 +17486,30 @@
         <v>69990</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G8" s="15">
         <v>1</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="J8" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>302</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>309</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P8" s="30"/>
     </row>
@@ -17545,7 +17518,7 @@
         <v>46087</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="27" t="s">
@@ -17555,7 +17528,7 @@
         <v>47900</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G9" s="15">
         <v>3</v>
@@ -17564,25 +17537,25 @@
         <v>40</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O9" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P9" s="30"/>
     </row>
@@ -17591,10 +17564,10 @@
         <v>46087</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>14</v>
@@ -17603,10 +17576,10 @@
         <v>53900</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H10" s="15">
         <v>65</v>
@@ -17615,17 +17588,17 @@
         <v>10</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O10" s="33"/>
       <c r="P10" s="30"/>
@@ -17635,10 +17608,10 @@
         <v>46087</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="20">
@@ -17650,20 +17623,20 @@
         <v>60</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="33"/>
       <c r="P11" s="30" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -17671,41 +17644,41 @@
         <v>46087</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="20">
         <v>54990</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="G12" s="15">
         <v>2</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="O12" s="33"/>
       <c r="P12" s="30" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -17713,41 +17686,41 @@
         <v>46087</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="20">
         <v>64990</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="G13" s="15">
         <v>2</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="O13" s="33"/>
       <c r="P13" s="30" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -17755,10 +17728,10 @@
         <v>46090</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>14</v>
@@ -17767,10 +17740,10 @@
         <v>56900</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H14" s="15">
         <v>75</v>
@@ -17779,22 +17752,22 @@
         <v>20</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O14" s="33" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P14" s="30"/>
     </row>
@@ -17803,10 +17776,10 @@
         <v>46090</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>14</v>
@@ -17815,10 +17788,10 @@
         <v>65900</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
@@ -17827,22 +17800,22 @@
         <v>20</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P15" s="30"/>
     </row>
@@ -17851,10 +17824,10 @@
         <v>46090</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>14</v>
@@ -17863,10 +17836,10 @@
         <v>75900</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H16" s="26">
         <v>130</v>
@@ -17875,22 +17848,22 @@
         <v>25</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P16" s="31"/>
     </row>
@@ -17899,10 +17872,10 @@
         <v>46090</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>14</v>
@@ -17911,32 +17884,32 @@
         <v>99900</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M17" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="O17" s="34" t="s">
         <v>330</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>337</v>
       </c>
       <c r="P17" s="31"/>
     </row>
@@ -17945,10 +17918,10 @@
         <v>46090</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>14</v>
@@ -17957,10 +17930,10 @@
         <v>62900</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H18" s="26">
         <v>60</v>
@@ -17969,22 +17942,22 @@
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="O18" s="34" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="P18" s="31"/>
     </row>
@@ -17993,10 +17966,10 @@
         <v>46090</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>14</v>
@@ -18005,10 +17978,10 @@
         <v>83900</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H19" s="26">
         <v>140</v>
@@ -18017,22 +17990,22 @@
         <v>25</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="O19" s="34" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="P19" s="31"/>
     </row>
@@ -18041,10 +18014,10 @@
         <v>46090</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D20" s="27" t="s">
         <v>14</v>
@@ -18053,10 +18026,10 @@
         <v>104900</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H20" s="26">
         <v>180</v>
@@ -18065,22 +18038,22 @@
         <v>50</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="O20" s="34" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="P20" s="31"/>
     </row>
@@ -18089,10 +18062,10 @@
         <v>46090</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>14</v>
@@ -18101,32 +18074,32 @@
         <v>128900</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O21" s="34" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="P21" s="31"/>
     </row>
@@ -18135,10 +18108,10 @@
         <v>46090</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D22" s="27" t="s">
         <v>14</v>
@@ -18147,10 +18120,10 @@
         <v>93900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H22" s="26">
         <v>60</v>
@@ -18159,22 +18132,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O22" s="34" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="P22" s="31"/>
     </row>
@@ -18183,10 +18156,10 @@
         <v>46090</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>14</v>
@@ -18195,10 +18168,10 @@
         <v>60900</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H23" s="26">
         <v>55</v>
@@ -18207,20 +18180,20 @@
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L23" s="26"/>
       <c r="M23" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O23" s="32" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="P23" s="31"/>
     </row>
@@ -18229,10 +18202,10 @@
         <v>46090</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D24" s="27" t="s">
         <v>14</v>
@@ -18241,10 +18214,10 @@
         <v>75900</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H24" s="26">
         <v>100</v>
@@ -18253,25 +18226,25 @@
         <v>25</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="105" x14ac:dyDescent="0.25">
@@ -18279,10 +18252,10 @@
         <v>46090</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>14</v>
@@ -18291,10 +18264,10 @@
         <v>86900</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H25" s="26">
         <v>105</v>
@@ -18303,25 +18276,25 @@
         <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="O25" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="P25" s="30" t="s">
         <v>341</v>
-      </c>
-      <c r="P25" s="30" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -18329,10 +18302,10 @@
         <v>46090</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D26" s="27" t="s">
         <v>14</v>
@@ -18349,21 +18322,21 @@
         <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L26" s="26"/>
       <c r="M26" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O26" s="32"/>
       <c r="P26" s="30" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18371,10 +18344,10 @@
         <v>46090</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D27" s="27" t="s">
         <v>14</v>
@@ -18391,21 +18364,21 @@
         <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O27" s="32"/>
       <c r="P27" s="30" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18413,10 +18386,10 @@
         <v>46090</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>14</v>
@@ -18433,21 +18406,21 @@
         <v>20</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L28" s="26"/>
       <c r="M28" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O28" s="32"/>
       <c r="P28" s="30" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18455,10 +18428,10 @@
         <v>46090</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>14</v>
@@ -18475,21 +18448,21 @@
         <v>10</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L29" s="26"/>
       <c r="M29" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O29" s="32"/>
       <c r="P29" s="31" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18497,10 +18470,10 @@
         <v>46090</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>14</v>
@@ -18509,10 +18482,10 @@
         <v>38900</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H30" s="26">
         <v>47</v>
@@ -18521,21 +18494,21 @@
         <v>5</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L30" s="26"/>
       <c r="M30" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O30" s="32"/>
       <c r="P30" s="30" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -18963,7 +18936,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -18989,37 +18962,37 @@
         <v>0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -19027,7 +19000,7 @@
         <v>46088</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -19046,19 +19019,19 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N3" s="14"/>
     </row>
@@ -19067,7 +19040,7 @@
         <v>46088</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -19085,22 +19058,22 @@
         <v>7</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N4" s="2"/>
     </row>
@@ -19109,7 +19082,7 @@
         <v>46088</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -19128,19 +19101,19 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -19149,7 +19122,7 @@
         <v>46088</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -19168,19 +19141,19 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N6" s="2"/>
     </row>
@@ -19189,7 +19162,7 @@
         <v>46088</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
@@ -19208,19 +19181,19 @@
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N7" s="2"/>
     </row>
@@ -19229,7 +19202,7 @@
         <v>46088</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
@@ -19248,19 +19221,19 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L8" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>376</v>
-      </c>
       <c r="M8" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N8" s="2"/>
     </row>
@@ -19269,7 +19242,7 @@
         <v>46088</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -19288,19 +19261,19 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N9" s="2"/>
     </row>
@@ -19309,7 +19282,7 @@
         <v>46088</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -19328,19 +19301,19 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N10" s="2"/>
     </row>
@@ -19349,7 +19322,7 @@
         <v>46088</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>14</v>
@@ -19368,19 +19341,19 @@
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N11" s="2"/>
     </row>
@@ -19389,7 +19362,7 @@
         <v>46088</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
@@ -19407,22 +19380,22 @@
         <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N12" s="2"/>
     </row>
@@ -19431,7 +19404,7 @@
         <v>46088</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>14</v>
@@ -19450,19 +19423,19 @@
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N13" s="2"/>
     </row>
@@ -19471,7 +19444,7 @@
         <v>46088</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>14</v>
@@ -19490,19 +19463,19 @@
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N14" s="2"/>
     </row>
@@ -19511,7 +19484,7 @@
         <v>46088</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -19530,19 +19503,19 @@
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N15" s="2"/>
     </row>
@@ -19551,7 +19524,7 @@
         <v>46088</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>22</v>
@@ -19570,19 +19543,19 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N16" s="2"/>
     </row>
@@ -19591,7 +19564,7 @@
         <v>46088</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
@@ -19610,19 +19583,19 @@
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -19631,7 +19604,7 @@
         <v>46088</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>22</v>
@@ -19650,19 +19623,19 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N18" s="2"/>
     </row>
@@ -19671,7 +19644,7 @@
         <v>46088</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>22</v>
@@ -19690,19 +19663,19 @@
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N19" s="2"/>
     </row>
@@ -19711,7 +19684,7 @@
         <v>46088</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
@@ -19730,19 +19703,19 @@
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N20" s="2"/>
     </row>
@@ -19751,7 +19724,7 @@
         <v>46088</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>22</v>
@@ -19770,19 +19743,19 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -19791,7 +19764,7 @@
         <v>46088</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>22</v>
@@ -19810,19 +19783,19 @@
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N22" s="2"/>
     </row>
@@ -19831,7 +19804,7 @@
         <v>46088</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>22</v>
@@ -19847,22 +19820,22 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N23" s="2"/>
     </row>
@@ -19871,7 +19844,7 @@
         <v>46088</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
@@ -19890,19 +19863,19 @@
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -19911,7 +19884,7 @@
         <v>46088</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>30</v>
@@ -19930,19 +19903,19 @@
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -19951,7 +19924,7 @@
         <v>46088</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>30</v>
@@ -19970,19 +19943,19 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -19991,7 +19964,7 @@
         <v>46088</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
@@ -20010,19 +19983,19 @@
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -20031,7 +20004,7 @@
         <v>46088</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>30</v>
@@ -20050,19 +20023,19 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -20071,7 +20044,7 @@
         <v>46088</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>30</v>
@@ -20090,19 +20063,19 @@
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -20111,7 +20084,7 @@
         <v>46088</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>30</v>
@@ -20129,22 +20102,22 @@
         <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -20153,7 +20126,7 @@
         <v>46088</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>30</v>
@@ -20172,19 +20145,19 @@
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N31" s="2"/>
     </row>
@@ -20193,7 +20166,7 @@
         <v>46088</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>30</v>
@@ -20212,19 +20185,19 @@
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -20233,7 +20206,7 @@
         <v>46088</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>30</v>
@@ -20252,19 +20225,19 @@
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -20273,7 +20246,7 @@
         <v>46088</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>30</v>
@@ -20292,19 +20265,19 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -20313,7 +20286,7 @@
         <v>46088</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>30</v>
@@ -20332,19 +20305,19 @@
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -20353,7 +20326,7 @@
         <v>46088</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>39</v>
@@ -20372,19 +20345,19 @@
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N36" s="2"/>
     </row>
@@ -20393,7 +20366,7 @@
         <v>46088</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>39</v>
@@ -20412,19 +20385,19 @@
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -20433,7 +20406,7 @@
         <v>46088</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>39</v>
@@ -20452,19 +20425,19 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -20473,7 +20446,7 @@
         <v>46088</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>39</v>
@@ -20492,19 +20465,19 @@
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M39" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -20513,7 +20486,7 @@
         <v>46088</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>39</v>
@@ -20532,19 +20505,19 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M40" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -20553,7 +20526,7 @@
         <v>46088</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>39</v>
@@ -20572,19 +20545,19 @@
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
     </row>
@@ -20593,7 +20566,7 @@
         <v>46088</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>39</v>
@@ -20612,19 +20585,19 @@
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -20633,7 +20606,7 @@
         <v>46088</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
@@ -20652,19 +20625,19 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N43" s="2"/>
     </row>
@@ -20673,7 +20646,7 @@
         <v>46088</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>39</v>
@@ -20692,19 +20665,19 @@
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N44" s="2"/>
     </row>
@@ -20713,7 +20686,7 @@
         <v>46088</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>39</v>
@@ -20732,19 +20705,19 @@
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
     </row>
@@ -20753,7 +20726,7 @@
         <v>46088</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>39</v>
@@ -20772,19 +20745,19 @@
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N46" s="2"/>
     </row>
@@ -20793,7 +20766,7 @@
         <v>46088</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>39</v>
@@ -20812,19 +20785,19 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N47" s="2"/>
     </row>
@@ -20833,7 +20806,7 @@
         <v>46088</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>45</v>
@@ -20852,19 +20825,19 @@
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M48" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N48" s="2"/>
     </row>
@@ -20873,7 +20846,7 @@
         <v>46088</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>45</v>
@@ -20892,19 +20865,19 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N49" s="2"/>
     </row>
@@ -20913,7 +20886,7 @@
         <v>46088</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>45</v>
@@ -20932,19 +20905,19 @@
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N50" s="2"/>
     </row>
@@ -20953,7 +20926,7 @@
         <v>46088</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>45</v>
@@ -20972,19 +20945,19 @@
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N51" s="2"/>
     </row>
@@ -20993,7 +20966,7 @@
         <v>46088</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>45</v>
@@ -21012,19 +20985,19 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N52" s="2"/>
     </row>
@@ -21033,7 +21006,7 @@
         <v>46088</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>45</v>
@@ -21052,19 +21025,19 @@
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N53" s="2"/>
     </row>
@@ -21073,7 +21046,7 @@
         <v>46088</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>45</v>
@@ -21092,19 +21065,19 @@
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N54" s="2"/>
     </row>
@@ -21113,7 +21086,7 @@
         <v>46088</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>45</v>
@@ -21132,19 +21105,19 @@
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N55" s="2"/>
     </row>
@@ -21153,7 +21126,7 @@
         <v>46088</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>45</v>
@@ -21172,19 +21145,19 @@
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N56" s="2"/>
     </row>
@@ -21193,7 +21166,7 @@
         <v>46088</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>45</v>
@@ -21212,19 +21185,19 @@
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N57" s="2"/>
     </row>
@@ -21233,7 +21206,7 @@
         <v>46090</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>14</v>
@@ -21245,27 +21218,27 @@
         <v>5000</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="G58" s="15">
         <v>3</v>
       </c>
       <c r="H58" s="15"/>
       <c r="I58" s="15" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M58" s="15"/>
       <c r="N58" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21273,7 +21246,7 @@
         <v>46090</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>14</v>
@@ -21285,27 +21258,27 @@
         <v>8000</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="G59" s="15">
         <v>6</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M59" s="15"/>
       <c r="N59" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21313,7 +21286,7 @@
         <v>46090</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>14</v>
@@ -21325,27 +21298,27 @@
         <v>9000</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G60" s="15">
         <v>7</v>
       </c>
       <c r="H60" s="15"/>
       <c r="I60" s="15" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L60" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M60" s="15"/>
       <c r="N60" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21353,7 +21326,7 @@
         <v>46090</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>14</v>
@@ -21365,27 +21338,27 @@
         <v>13000</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G61" s="15">
         <v>10</v>
       </c>
       <c r="H61" s="15"/>
       <c r="I61" s="15" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M61" s="15"/>
       <c r="N61" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21393,7 +21366,7 @@
         <v>46090</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>14</v>
@@ -21405,27 +21378,27 @@
         <v>23000</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="G62" s="15">
         <v>20</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="15" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M62" s="15"/>
       <c r="N62" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21433,7 +21406,7 @@
         <v>46090</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>14</v>
@@ -21445,27 +21418,27 @@
         <v>33000</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G63" s="15">
         <v>30</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="15" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M63" s="15"/>
       <c r="N63" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21473,7 +21446,7 @@
         <v>46090</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>14</v>
@@ -21485,27 +21458,27 @@
         <v>43000</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G64" s="15">
         <v>30</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="15" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M64" s="15"/>
       <c r="N64" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21513,7 +21486,7 @@
         <v>46090</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>14</v>
@@ -21525,27 +21498,27 @@
         <v>100000</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G65" s="15">
         <v>30</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="15" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M65" s="15"/>
       <c r="N65" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21553,7 +21526,7 @@
         <v>46090</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>14</v>
@@ -21565,25 +21538,25 @@
         <v>13000</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G66" s="15">
         <v>7</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K66" s="15"/>
       <c r="L66" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M66" s="15"/>
       <c r="N66" s="15" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21591,7 +21564,7 @@
         <v>46090</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>14</v>
@@ -21603,25 +21576,25 @@
         <v>23000</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G67" s="15">
         <v>15</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K67" s="15"/>
       <c r="L67" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M67" s="15"/>
       <c r="N67" s="15" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21629,7 +21602,7 @@
         <v>46090</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>14</v>
@@ -21641,25 +21614,25 @@
         <v>33000</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G68" s="15">
         <v>30</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K68" s="15"/>
       <c r="L68" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M68" s="15"/>
       <c r="N68" s="15" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21667,7 +21640,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>14</v>
@@ -21679,27 +21652,27 @@
         <v>4500</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G69" s="15">
         <v>7</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="15" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M69" s="15"/>
       <c r="N69" s="15" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -21862,6 +21835,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008132F03F7BAE544691E1D8ED0BBAB87D" ma:contentTypeVersion="21" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e484fd9c9d78115df5d140a0e15bddb5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="612f0692-a35d-4227-ae2b-09b69c7561dc" xmlns:ns3="c9fa2ff5-4241-4755-bdec-11c5f369898d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60915895e4af9a5e40828d772a1103ab" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -22139,30 +22135,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
+    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B03BB360-2000-407D-9849-F3FC94EAD1FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22180,24 +22173,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
-    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/Benchmarking.xlsx
+++ b/assets/Benchmarking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO NO BORRAR\Documents\GitHub\asesores\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363008FC-35CB-42BC-86E0-A3A48175F96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95CBFE-FC47-4168-9216-FF421C82A6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{F3156A63-ABA6-4DCB-AB8A-B4C8C83E2F35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F3156A63-ABA6-4DCB-AB8A-B4C8C83E2F35}"/>
   </bookViews>
   <sheets>
     <sheet name="FILTRO" sheetId="9" r:id="rId1"/>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="463">
   <si>
     <t>Operador</t>
   </si>
@@ -767,9 +767,6 @@
     <t>Carlos Franco</t>
   </si>
   <si>
-    <t>$86.436</t>
-  </si>
-  <si>
     <t>Paga primera factura a $66.489</t>
   </si>
   <si>
@@ -782,9 +779,6 @@
     <t>Sencillo Internet</t>
   </si>
   <si>
-    <t>$49.900</t>
-  </si>
-  <si>
     <t>Sin cargo de conexion, sin clausula de permanencia y compra ahpra y paga el proximo mes</t>
   </si>
   <si>
@@ -794,61 +788,37 @@
     <t>Operador Bitwan (INSITEL )</t>
   </si>
   <si>
-    <t>$74.800</t>
-  </si>
-  <si>
     <t>Basica</t>
   </si>
   <si>
     <t>TV por Streaming, 2 pantallas con 110 canales</t>
   </si>
   <si>
-    <t>$ 106.990</t>
-  </si>
-  <si>
     <t>Sin Cargo de Conexión, Compra hoy y paga el proximo mes, 50% de descuento mes 2 ($53.495)</t>
   </si>
   <si>
-    <t>$ 124.990</t>
-  </si>
-  <si>
     <t>Sin Cargo de Conexión, Compra hoy y paga el proximo mes, 50% de descuento mes 2 ($62.495)</t>
   </si>
   <si>
     <t>Escoger entre Win, Disney O NetFlix</t>
   </si>
   <si>
-    <t>$ 139.990</t>
-  </si>
-  <si>
     <t>Sin Cargo de Conexión, Compra hoy y paga el proximo mes, 50% de descuento mes 2 ($69.995)</t>
   </si>
   <si>
-    <t>$ 157.990</t>
-  </si>
-  <si>
     <t>Sin Cargo de Conexión, Compra hoy y paga el proximo mes, 50% de descuento mes 2 ($78.995)</t>
   </si>
   <si>
     <t> </t>
   </si>
   <si>
-    <t>$ 69,900</t>
-  </si>
-  <si>
     <t>Sin Cargo de Conexión, y sin clausula de permanencia</t>
   </si>
   <si>
     <t>MARZO</t>
   </si>
   <si>
-    <t>$ 55,000</t>
-  </si>
-  <si>
     <t>80 MG</t>
-  </si>
-  <si>
-    <t>$ 54,900</t>
   </si>
   <si>
     <t>70 MG</t>
@@ -7258,7 +7228,7 @@
         <v>88</v>
       </c>
       <c r="K2" s="54" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="L2" s="54" t="s">
         <v>89</v>
@@ -7288,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="U2" s="54" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="V2" s="54" t="s">
         <v>97</v>
@@ -10657,7 +10627,7 @@
         <v>86436</v>
       </c>
       <c r="K51" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L51" s="56" t="s">
         <v>102</v>
@@ -10666,10 +10636,10 @@
         <v>151</v>
       </c>
       <c r="N51" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="O51" s="56" t="s">
         <v>192</v>
-      </c>
-      <c r="O51" s="56" t="s">
-        <v>193</v>
       </c>
       <c r="P51" s="56">
         <v>1</v>
@@ -10711,19 +10681,19 @@
         <v>17</v>
       </c>
       <c r="I52" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="J52" s="57">
+        <v>49900</v>
+      </c>
+      <c r="K52" s="56" t="s">
         <v>194</v>
-      </c>
-      <c r="J52" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="K52" s="56" t="s">
-        <v>196</v>
       </c>
       <c r="L52" s="56" t="s">
         <v>102</v>
       </c>
       <c r="M52" s="56" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N52" s="56" t="s">
         <v>138</v>
@@ -10743,7 +10713,7 @@
       <c r="U52" s="58"/>
       <c r="V52" s="56"/>
       <c r="W52" s="56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X52" s="56" t="s">
         <v>21</v>
@@ -10777,11 +10747,11 @@
       <c r="I53" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="J53" s="57" t="s">
+      <c r="J53" s="57">
+        <v>86436</v>
+      </c>
+      <c r="K53" s="56" t="s">
         <v>190</v>
-      </c>
-      <c r="K53" s="56" t="s">
-        <v>191</v>
       </c>
       <c r="L53" s="56" t="s">
         <v>102</v>
@@ -10790,10 +10760,10 @@
         <v>151</v>
       </c>
       <c r="N53" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="O53" s="56" t="s">
         <v>192</v>
-      </c>
-      <c r="O53" s="56" t="s">
-        <v>193</v>
       </c>
       <c r="P53" s="56">
         <v>1</v>
@@ -10837,11 +10807,11 @@
       <c r="I54" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="J54" s="57" t="s">
-        <v>199</v>
+      <c r="J54" s="57">
+        <v>74800</v>
       </c>
       <c r="K54" s="56" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L54" s="56" t="s">
         <v>102</v>
@@ -10850,10 +10820,10 @@
         <v>166</v>
       </c>
       <c r="N54" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="O54" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P54" s="56" t="s">
         <v>138</v>
@@ -10867,7 +10837,7 @@
       <c r="U54" s="58"/>
       <c r="V54" s="56"/>
       <c r="W54" s="56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X54" s="56" t="s">
         <v>21</v>
@@ -10901,11 +10871,11 @@
       <c r="I55" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="J55" s="77" t="s">
-        <v>202</v>
+      <c r="J55" s="77">
+        <v>106990</v>
       </c>
       <c r="K55" s="77" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L55" s="77" t="s">
         <v>102</v>
@@ -10959,11 +10929,11 @@
       <c r="I56" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="J56" s="77" t="s">
-        <v>204</v>
+      <c r="J56" s="77">
+        <v>124990</v>
       </c>
       <c r="K56" s="77" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L56" s="77" t="s">
         <v>102</v>
@@ -10983,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="U56" s="77" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="V56" s="77" t="s">
         <v>139</v>
@@ -11021,11 +10991,11 @@
       <c r="I57" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="J57" s="77" t="s">
-        <v>207</v>
+      <c r="J57" s="77">
+        <v>139990</v>
       </c>
       <c r="K57" s="77" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="L57" s="77" t="s">
         <v>102</v>
@@ -11081,11 +11051,11 @@
       <c r="I58" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="J58" s="77" t="s">
-        <v>209</v>
+      <c r="J58" s="77">
+        <v>157990</v>
       </c>
       <c r="K58" s="77" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="L58" s="77" t="s">
         <v>102</v>
@@ -11107,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="50" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="V58" s="50" t="s">
         <v>139</v>
@@ -11143,49 +11113,49 @@
         <v>17</v>
       </c>
       <c r="I59" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="J59" s="77" t="s">
-        <v>212</v>
+        <v>204</v>
+      </c>
+      <c r="J59" s="77">
+        <v>69900</v>
       </c>
       <c r="K59" s="77" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L59" s="77" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M59" s="77" t="s">
         <v>157</v>
       </c>
       <c r="N59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W59" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="X59" s="77" t="s">
         <v>21</v>
@@ -11219,47 +11189,47 @@
       <c r="I60" s="77" t="s">
         <v>187</v>
       </c>
-      <c r="J60" s="77" t="s">
-        <v>215</v>
+      <c r="J60" s="77">
+        <v>55000</v>
       </c>
       <c r="K60" s="77" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L60" s="77" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M60" s="77" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="N60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W60" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="X60" s="77" t="s">
         <v>21</v>
@@ -11291,49 +11261,49 @@
         <v>17</v>
       </c>
       <c r="I61" s="77" t="s">
-        <v>211</v>
-      </c>
-      <c r="J61" s="77" t="s">
-        <v>217</v>
+        <v>204</v>
+      </c>
+      <c r="J61" s="77">
+        <v>54900</v>
       </c>
       <c r="K61" s="77" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L61" s="77" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M61" s="77" t="s">
         <v>166</v>
       </c>
       <c r="N61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W61" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="X61" s="77" t="s">
         <v>21</v>
@@ -11365,49 +11335,49 @@
         <v>17</v>
       </c>
       <c r="I62" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="J62" s="77" t="s">
-        <v>217</v>
+        <v>204</v>
+      </c>
+      <c r="J62" s="77">
+        <v>54900</v>
       </c>
       <c r="K62" s="77" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L62" s="77" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M62" s="77" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="N62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V62" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W62" s="50" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X62" s="77" t="s">
         <v>21</v>
@@ -11418,7 +11388,7 @@
         <v>46092</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C63" s="44" t="s">
         <v>14</v>
@@ -11490,7 +11460,7 @@
         <v>46092</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C64" s="44" t="s">
         <v>14</v>
@@ -11562,7 +11532,7 @@
         <v>46092</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C65" s="44" t="s">
         <v>14</v>
@@ -11630,7 +11600,7 @@
         <v>46092</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C66" s="44" t="s">
         <v>14</v>
@@ -11690,7 +11660,7 @@
         <v>46092</v>
       </c>
       <c r="B67" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C67" s="44" t="s">
         <v>14</v>
@@ -11756,7 +11726,7 @@
         <v>46092</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C68" s="44" t="s">
         <v>14</v>
@@ -11777,19 +11747,19 @@
         <v>17</v>
       </c>
       <c r="I68" s="51" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J68" s="52">
         <v>49900</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L68" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M68" s="51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N68" s="51" t="s">
         <v>138</v>
@@ -11809,7 +11779,7 @@
       <c r="U68" s="53"/>
       <c r="V68" s="51"/>
       <c r="W68" s="51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X68" s="51" t="s">
         <v>21</v>
@@ -11820,7 +11790,7 @@
         <v>46092</v>
       </c>
       <c r="B69" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C69" s="44" t="s">
         <v>14</v>
@@ -11847,7 +11817,7 @@
         <v>86436</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L69" s="51" t="s">
         <v>102</v>
@@ -11856,10 +11826,10 @@
         <v>151</v>
       </c>
       <c r="N69" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="O69" s="51" t="s">
         <v>192</v>
-      </c>
-      <c r="O69" s="51" t="s">
-        <v>193</v>
       </c>
       <c r="P69" s="51">
         <v>1</v>
@@ -11880,7 +11850,7 @@
         <v>46092</v>
       </c>
       <c r="B70" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C70" s="44" t="s">
         <v>14</v>
@@ -11901,19 +11871,19 @@
         <v>17</v>
       </c>
       <c r="I70" s="51" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J70" s="52">
         <v>49900</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L70" s="51" t="s">
         <v>102</v>
       </c>
       <c r="M70" s="51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N70" s="51" t="s">
         <v>138</v>
@@ -11933,7 +11903,7 @@
       <c r="U70" s="53"/>
       <c r="V70" s="51"/>
       <c r="W70" s="51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X70" s="51" t="s">
         <v>21</v>
@@ -11944,7 +11914,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C71" s="44" t="s">
         <v>14</v>
@@ -11971,7 +11941,7 @@
         <v>86436</v>
       </c>
       <c r="K71" s="51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L71" s="51" t="s">
         <v>102</v>
@@ -11980,10 +11950,10 @@
         <v>151</v>
       </c>
       <c r="N71" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="O71" s="51" t="s">
         <v>192</v>
-      </c>
-      <c r="O71" s="51" t="s">
-        <v>193</v>
       </c>
       <c r="P71" s="51">
         <v>1</v>
@@ -12004,7 +11974,7 @@
         <v>46092</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C72" s="44" t="s">
         <v>14</v>
@@ -12025,49 +11995,49 @@
         <v>17</v>
       </c>
       <c r="I72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J72" s="50">
         <v>54900</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L72" s="50" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M72" s="50" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="N72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V72" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W72" s="50" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X72" s="50" t="s">
         <v>21</v>
@@ -12078,7 +12048,7 @@
         <v>46092</v>
       </c>
       <c r="B73" s="50" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C73" s="44" t="s">
         <v>14</v>
@@ -12099,49 +12069,49 @@
         <v>17</v>
       </c>
       <c r="I73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J73" s="50">
         <v>54900</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L73" s="50" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M73" s="50" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="N73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V73" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W73" s="50" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X73" s="50" t="s">
         <v>21</v>
@@ -12152,7 +12122,7 @@
         <v>46092</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C74" s="44" t="s">
         <v>14</v>
@@ -12173,49 +12143,49 @@
         <v>17</v>
       </c>
       <c r="I74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J74" s="50">
         <v>54900</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L74" s="50" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M74" s="50" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="N74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="R74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="U74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="V74" s="78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="W74" s="50" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X74" s="50" t="s">
         <v>21</v>
@@ -12226,7 +12196,7 @@
         <v>46092</v>
       </c>
       <c r="B75" s="50" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C75" s="44" t="s">
         <v>14</v>
@@ -12251,10 +12221,10 @@
         <v>94990</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="L75" s="51" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="M75" s="51">
         <v>949990</v>
@@ -12284,7 +12254,7 @@
         <v>138</v>
       </c>
       <c r="V75" s="51" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="W75" s="51"/>
       <c r="X75" s="51"/>
@@ -12385,19 +12355,19 @@
         <v>17</v>
       </c>
       <c r="I77" s="51" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="J77" s="52">
         <v>75000</v>
       </c>
       <c r="K77" s="51" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L77" s="51" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="M77" s="51" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N77" s="51" t="s">
         <v>138</v>
@@ -12427,7 +12397,7 @@
         <v>138</v>
       </c>
       <c r="W77" s="51" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="X77" s="51" t="s">
         <v>21</v>
@@ -12459,19 +12429,19 @@
         <v>17</v>
       </c>
       <c r="I78" s="51" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="J78" s="52">
         <v>120000</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L78" s="51" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="M78" s="51" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="N78" s="51" t="s">
         <v>138</v>
@@ -12483,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="53" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="R78" s="53" t="s">
         <v>138</v>
@@ -12501,7 +12471,7 @@
         <v>138</v>
       </c>
       <c r="W78" s="51" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="X78" s="51" t="s">
         <v>21</v>
@@ -12512,7 +12482,7 @@
         <v>46092</v>
       </c>
       <c r="B79" s="50" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C79" s="44" t="s">
         <v>14</v>
@@ -12533,16 +12503,16 @@
         <v>17</v>
       </c>
       <c r="I79" s="51" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="J79" s="52">
         <v>84900</v>
       </c>
       <c r="K79" s="51" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="L79" s="51" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="M79" s="51" t="s">
         <v>151</v>
@@ -12605,20 +12575,20 @@
         <v>17</v>
       </c>
       <c r="I80" s="51" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="J80" s="52">
         <v>24000</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L80" s="51"/>
       <c r="M80" s="51" t="s">
         <v>138</v>
       </c>
       <c r="N80" s="51" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="O80" s="51">
         <v>100</v>
@@ -12645,7 +12615,7 @@
         <v>138</v>
       </c>
       <c r="W80" s="51" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="X80" s="51" t="s">
         <v>21</v>
@@ -12677,22 +12647,22 @@
         <v>24</v>
       </c>
       <c r="I81" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J81" s="52">
         <v>60000</v>
       </c>
       <c r="K81" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L81" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M81" s="51" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N81" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O81" s="51">
         <v>80</v>
@@ -12719,7 +12689,7 @@
         <v>138</v>
       </c>
       <c r="W81" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X81" s="51" t="s">
         <v>21</v>
@@ -12751,22 +12721,22 @@
         <v>24</v>
       </c>
       <c r="I82" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J82" s="52">
         <v>75800</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L82" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M82" s="51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N82" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O82" s="51">
         <v>80</v>
@@ -12793,7 +12763,7 @@
         <v>138</v>
       </c>
       <c r="W82" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X82" s="51" t="s">
         <v>21</v>
@@ -12825,22 +12795,22 @@
         <v>24</v>
       </c>
       <c r="I83" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J83" s="52">
         <v>97800</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L83" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M83" s="51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="N83" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O83" s="51">
         <v>80</v>
@@ -12867,7 +12837,7 @@
         <v>138</v>
       </c>
       <c r="W83" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X83" s="51" t="s">
         <v>21</v>
@@ -12878,7 +12848,7 @@
         <v>46092</v>
       </c>
       <c r="B84" s="50" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C84" s="44" t="s">
         <v>14</v>
@@ -12934,22 +12904,22 @@
         <v>24</v>
       </c>
       <c r="I85" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J85" s="52">
         <v>60000</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L85" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M85" s="51" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N85" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O85" s="51">
         <v>80</v>
@@ -12976,7 +12946,7 @@
         <v>138</v>
       </c>
       <c r="W85" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X85" s="51" t="s">
         <v>21</v>
@@ -13008,22 +12978,22 @@
         <v>24</v>
       </c>
       <c r="I86" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J86" s="52">
         <v>75800</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L86" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M86" s="51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N86" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O86" s="51">
         <v>80</v>
@@ -13050,7 +13020,7 @@
         <v>138</v>
       </c>
       <c r="W86" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X86" s="51" t="s">
         <v>21</v>
@@ -13082,22 +13052,22 @@
         <v>24</v>
       </c>
       <c r="I87" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J87" s="52">
         <v>97800</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L87" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M87" s="51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="N87" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O87" s="51">
         <v>80</v>
@@ -13124,7 +13094,7 @@
         <v>138</v>
       </c>
       <c r="W87" s="51" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X87" s="51" t="s">
         <v>21</v>
@@ -13156,22 +13126,22 @@
         <v>17</v>
       </c>
       <c r="I88" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J88" s="52">
         <v>78000</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L88" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M88" s="51" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N88" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O88" s="51" t="s">
         <v>138</v>
@@ -13198,7 +13168,7 @@
         <v>138</v>
       </c>
       <c r="W88" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X88" s="51" t="s">
         <v>21</v>
@@ -13230,22 +13200,22 @@
         <v>17</v>
       </c>
       <c r="I89" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J89" s="52">
         <v>99000</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L89" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M89" s="51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N89" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O89" s="51" t="s">
         <v>138</v>
@@ -13272,7 +13242,7 @@
         <v>138</v>
       </c>
       <c r="W89" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X89" s="51" t="s">
         <v>21</v>
@@ -13304,22 +13274,22 @@
         <v>17</v>
       </c>
       <c r="I90" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J90" s="52">
         <v>119000</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L90" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M90" s="51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="N90" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O90" s="51" t="s">
         <v>138</v>
@@ -13346,7 +13316,7 @@
         <v>138</v>
       </c>
       <c r="W90" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X90" s="51" t="s">
         <v>21</v>
@@ -13378,22 +13348,22 @@
         <v>17</v>
       </c>
       <c r="I91" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J91" s="52">
         <v>61000</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L91" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M91" s="51" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="N91" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O91" s="51" t="s">
         <v>138</v>
@@ -13420,7 +13390,7 @@
         <v>138</v>
       </c>
       <c r="W91" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X91" s="51" t="s">
         <v>21</v>
@@ -13452,22 +13422,22 @@
         <v>17</v>
       </c>
       <c r="I92" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J92" s="52">
         <v>78000</v>
       </c>
       <c r="K92" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L92" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M92" s="51" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N92" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O92" s="51" t="s">
         <v>138</v>
@@ -13494,7 +13464,7 @@
         <v>138</v>
       </c>
       <c r="W92" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X92" s="51" t="s">
         <v>21</v>
@@ -13526,22 +13496,22 @@
         <v>17</v>
       </c>
       <c r="I93" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J93" s="52">
         <v>99000</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L93" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M93" s="51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N93" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O93" s="51" t="s">
         <v>138</v>
@@ -13568,7 +13538,7 @@
         <v>138</v>
       </c>
       <c r="W93" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X93" s="51" t="s">
         <v>21</v>
@@ -13600,22 +13570,22 @@
         <v>17</v>
       </c>
       <c r="I94" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J94" s="52">
         <v>119000</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L94" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M94" s="51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="N94" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O94" s="51" t="s">
         <v>138</v>
@@ -13642,7 +13612,7 @@
         <v>138</v>
       </c>
       <c r="W94" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X94" s="51" t="s">
         <v>21</v>
@@ -13674,22 +13644,22 @@
         <v>17</v>
       </c>
       <c r="I95" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J95" s="52">
         <v>61000</v>
       </c>
       <c r="K95" s="51" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L95" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M95" s="51" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="N95" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="O95" s="51" t="s">
         <v>138</v>
@@ -13716,7 +13686,7 @@
         <v>138</v>
       </c>
       <c r="W95" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="X95" s="51" t="s">
         <v>21</v>
@@ -13748,22 +13718,22 @@
         <v>24</v>
       </c>
       <c r="I96" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J96" s="61">
         <v>65.567999999999998</v>
       </c>
       <c r="K96" s="51" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L96" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M96" s="56" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="N96" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O96" s="56">
         <v>40</v>
@@ -13790,7 +13760,7 @@
         <v>138</v>
       </c>
       <c r="W96" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X96" s="51" t="s">
         <v>21</v>
@@ -13822,20 +13792,20 @@
         <v>24</v>
       </c>
       <c r="I97" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J97" s="57"/>
       <c r="K97" s="51" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L97" s="51" t="s">
         <v>138</v>
       </c>
       <c r="M97" s="56" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="N97" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O97" s="56">
         <v>40</v>
@@ -13862,7 +13832,7 @@
         <v>138</v>
       </c>
       <c r="W97" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X97" s="51" t="s">
         <v>21</v>
@@ -13894,7 +13864,7 @@
         <v>24</v>
       </c>
       <c r="I98" s="56" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J98" s="57">
         <v>109900</v>
@@ -13906,10 +13876,10 @@
         <v>138</v>
       </c>
       <c r="M98" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N98" s="56" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O98" s="56" t="s">
         <v>138</v>
@@ -13936,7 +13906,7 @@
         <v>138</v>
       </c>
       <c r="W98" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X98" s="56" t="s">
         <v>21</v>
@@ -13968,7 +13938,7 @@
         <v>24</v>
       </c>
       <c r="I99" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J99" s="57">
         <v>109900</v>
@@ -13980,10 +13950,10 @@
         <v>138</v>
       </c>
       <c r="M99" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N99" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="O99" s="56" t="s">
         <v>138</v>
@@ -14010,7 +13980,7 @@
         <v>138</v>
       </c>
       <c r="W99" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X99" s="56" t="s">
         <v>21</v>
@@ -14042,7 +14012,7 @@
         <v>24</v>
       </c>
       <c r="I100" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J100" s="57">
         <v>109900</v>
@@ -14054,10 +14024,10 @@
         <v>138</v>
       </c>
       <c r="M100" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N100" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O100" s="56" t="s">
         <v>138</v>
@@ -14084,7 +14054,7 @@
         <v>138</v>
       </c>
       <c r="W100" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X100" s="56" t="s">
         <v>21</v>
@@ -14116,7 +14086,7 @@
         <v>24</v>
       </c>
       <c r="I101" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J101" s="61">
         <v>84.850999999999999</v>
@@ -14128,10 +14098,10 @@
         <v>138</v>
       </c>
       <c r="M101" s="56" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N101" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O101" s="56">
         <v>40</v>
@@ -14158,7 +14128,7 @@
         <v>138</v>
       </c>
       <c r="W101" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X101" s="56" t="s">
         <v>21</v>
@@ -14190,7 +14160,7 @@
         <v>24</v>
       </c>
       <c r="I102" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J102" s="61">
         <v>109171</v>
@@ -14202,10 +14172,10 @@
         <v>138</v>
       </c>
       <c r="M102" s="56" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="N102" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O102" s="56">
         <v>40</v>
@@ -14232,7 +14202,7 @@
         <v>138</v>
       </c>
       <c r="W102" s="56" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="X102" s="56" t="s">
         <v>21</v>
@@ -14264,7 +14234,7 @@
         <v>24</v>
       </c>
       <c r="I103" s="56" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J103" s="57">
         <v>99900</v>
@@ -14276,10 +14246,10 @@
         <v>138</v>
       </c>
       <c r="M103" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N103" s="56" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O103" s="56" t="s">
         <v>138</v>
@@ -14306,7 +14276,7 @@
         <v>138</v>
       </c>
       <c r="W103" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X103" s="56" t="s">
         <v>21</v>
@@ -14338,7 +14308,7 @@
         <v>24</v>
       </c>
       <c r="I104" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J104" s="57">
         <v>99900</v>
@@ -14350,10 +14320,10 @@
         <v>138</v>
       </c>
       <c r="M104" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N104" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="O104" s="56" t="s">
         <v>138</v>
@@ -14380,7 +14350,7 @@
         <v>138</v>
       </c>
       <c r="W104" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X104" s="56" t="s">
         <v>21</v>
@@ -14412,7 +14382,7 @@
         <v>24</v>
       </c>
       <c r="I105" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J105" s="57">
         <v>99900</v>
@@ -14424,10 +14394,10 @@
         <v>138</v>
       </c>
       <c r="M105" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N105" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O105" s="56" t="s">
         <v>138</v>
@@ -14454,7 +14424,7 @@
         <v>138</v>
       </c>
       <c r="W105" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X105" s="56" t="s">
         <v>21</v>
@@ -14486,7 +14456,7 @@
         <v>24</v>
       </c>
       <c r="I106" s="56" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J106" s="57">
         <v>109900</v>
@@ -14498,10 +14468,10 @@
         <v>138</v>
       </c>
       <c r="M106" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N106" s="56" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O106" s="56" t="s">
         <v>138</v>
@@ -14528,7 +14498,7 @@
         <v>138</v>
       </c>
       <c r="W106" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X106" s="56" t="s">
         <v>21</v>
@@ -14560,7 +14530,7 @@
         <v>24</v>
       </c>
       <c r="I107" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J107" s="57">
         <v>109900</v>
@@ -14572,10 +14542,10 @@
         <v>138</v>
       </c>
       <c r="M107" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N107" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="O107" s="56" t="s">
         <v>138</v>
@@ -14602,7 +14572,7 @@
         <v>138</v>
       </c>
       <c r="W107" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X107" s="56" t="s">
         <v>21</v>
@@ -14634,7 +14604,7 @@
         <v>24</v>
       </c>
       <c r="I108" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J108" s="57">
         <v>109900</v>
@@ -14646,10 +14616,10 @@
         <v>138</v>
       </c>
       <c r="M108" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N108" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O108" s="56" t="s">
         <v>138</v>
@@ -14676,7 +14646,7 @@
         <v>138</v>
       </c>
       <c r="W108" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="X108" s="56" t="s">
         <v>21</v>
@@ -14708,7 +14678,7 @@
         <v>24</v>
       </c>
       <c r="I109" s="56" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J109" s="57">
         <v>99900</v>
@@ -14720,10 +14690,10 @@
         <v>138</v>
       </c>
       <c r="M109" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N109" s="56" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O109" s="56" t="s">
         <v>138</v>
@@ -14750,7 +14720,7 @@
         <v>138</v>
       </c>
       <c r="W109" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X109" s="56" t="s">
         <v>21</v>
@@ -14782,7 +14752,7 @@
         <v>24</v>
       </c>
       <c r="I110" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J110" s="57">
         <v>99900</v>
@@ -14794,10 +14764,10 @@
         <v>138</v>
       </c>
       <c r="M110" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="O110" s="56" t="s">
         <v>138</v>
@@ -14824,7 +14794,7 @@
         <v>138</v>
       </c>
       <c r="W110" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X110" s="56" t="s">
         <v>21</v>
@@ -14856,7 +14826,7 @@
         <v>24</v>
       </c>
       <c r="I111" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J111" s="57">
         <v>99900</v>
@@ -14868,10 +14838,10 @@
         <v>138</v>
       </c>
       <c r="M111" s="56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O111" s="56" t="s">
         <v>138</v>
@@ -14898,7 +14868,7 @@
         <v>138</v>
       </c>
       <c r="W111" s="56" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="X111" s="56" t="s">
         <v>21</v>
@@ -14909,7 +14879,7 @@
         <v>46092</v>
       </c>
       <c r="B112" s="47" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C112" s="44" t="s">
         <v>14</v>
@@ -14930,7 +14900,7 @@
         <v>32</v>
       </c>
       <c r="I112" s="56" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J112" s="57">
         <v>119900</v>
@@ -14942,10 +14912,10 @@
         <v>138</v>
       </c>
       <c r="M112" s="56" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="O112" s="56">
         <v>156</v>
@@ -14966,7 +14936,7 @@
         <v>138</v>
       </c>
       <c r="U112" s="56" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="V112" s="56" t="s">
         <v>138</v>
@@ -14983,7 +14953,7 @@
         <v>46092</v>
       </c>
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C113" s="44" t="s">
         <v>14</v>
@@ -15004,7 +14974,7 @@
         <v>38</v>
       </c>
       <c r="I113" s="56" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="J113" s="57">
         <v>89900</v>
@@ -15040,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="U113" s="56" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="V113" s="56" t="s">
         <v>138</v>
@@ -15057,7 +15027,7 @@
         <v>46092</v>
       </c>
       <c r="B114" s="47" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C114" s="44" t="s">
         <v>37</v>
@@ -15078,49 +15048,49 @@
         <v>17</v>
       </c>
       <c r="I114" s="56" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="J114" s="57">
         <v>63000</v>
       </c>
       <c r="K114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M114" s="56" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="P114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Q114" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R114" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S114" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="T114" s="58">
         <v>1</v>
       </c>
       <c r="U114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V114" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W114" s="56" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="X114" s="56" t="s">
         <v>42</v>
@@ -15131,7 +15101,7 @@
         <v>46092</v>
       </c>
       <c r="B115" s="47" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C115" s="44" t="s">
         <v>37</v>
@@ -15152,49 +15122,49 @@
         <v>17</v>
       </c>
       <c r="I115" s="56" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="J115" s="57">
         <v>100000</v>
       </c>
       <c r="K115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M115" s="56" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="P115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Q115" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R115" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S115" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="T115" s="58">
         <v>1</v>
       </c>
       <c r="U115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V115" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W115" s="56" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="X115" s="56" t="s">
         <v>42</v>
@@ -15205,7 +15175,7 @@
         <v>46092</v>
       </c>
       <c r="B116" s="47" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C116" s="44" t="s">
         <v>37</v>
@@ -15226,49 +15196,49 @@
         <v>17</v>
       </c>
       <c r="I116" s="56" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="J116" s="57">
         <v>75000</v>
       </c>
       <c r="K116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M116" s="56" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="P116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Q116" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R116" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S116" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="T116" s="58">
         <v>1</v>
       </c>
       <c r="U116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V116" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W116" s="56" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="X116" s="56" t="s">
         <v>42</v>
@@ -15279,7 +15249,7 @@
         <v>46092</v>
       </c>
       <c r="B117" s="47" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C117" s="44" t="s">
         <v>59</v>
@@ -15300,22 +15270,22 @@
         <v>24</v>
       </c>
       <c r="I117" s="56" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J117" s="57">
         <v>99000</v>
       </c>
       <c r="K117" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L117" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M117" s="56" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="O117" s="56">
         <v>80</v>
@@ -15324,25 +15294,25 @@
         <v>1</v>
       </c>
       <c r="Q117" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R117" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S117" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="T117" s="58">
         <v>1</v>
       </c>
       <c r="U117" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V117" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W117" s="56" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="X117" s="56" t="s">
         <v>42</v>
@@ -15353,7 +15323,7 @@
         <v>46092</v>
       </c>
       <c r="B118" s="47" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C118" s="44" t="s">
         <v>59</v>
@@ -15374,49 +15344,49 @@
         <v>17</v>
       </c>
       <c r="I118" s="56" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="J118" s="57">
         <v>65000</v>
       </c>
       <c r="K118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M118" s="56" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="P118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Q118" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R118" s="58" t="s">
         <v>25</v>
       </c>
       <c r="S118" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="T118" s="58">
         <v>1</v>
       </c>
       <c r="U118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W118" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="X118" s="56" t="s">
         <v>21</v>
@@ -15427,7 +15397,7 @@
         <v>46092</v>
       </c>
       <c r="B119" s="47" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C119" s="44" t="s">
         <v>47</v>
@@ -15460,19 +15430,19 @@
         <v>138</v>
       </c>
       <c r="M119" s="56" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O119" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="P119" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Q119" s="58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="R119" s="58" t="s">
         <v>25</v>
@@ -15484,13 +15454,13 @@
         <v>138</v>
       </c>
       <c r="U119" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="V119" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W119" s="56" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="X119" s="56" t="s">
         <v>42</v>
@@ -15501,7 +15471,7 @@
         <v>46092</v>
       </c>
       <c r="B120" s="47" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C120" s="44" t="s">
         <v>47</v>
@@ -15522,7 +15492,7 @@
         <v>24</v>
       </c>
       <c r="I120" s="56" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="J120" s="57">
         <v>69000</v>
@@ -15534,10 +15504,10 @@
         <v>138</v>
       </c>
       <c r="M120" s="56" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="O120" s="56">
         <v>110</v>
@@ -15564,7 +15534,7 @@
         <v>138</v>
       </c>
       <c r="W120" s="56" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="X120" s="56" t="s">
         <v>42</v>
@@ -15575,7 +15545,7 @@
         <v>46092</v>
       </c>
       <c r="B121" s="47" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C121" s="44" t="s">
         <v>47</v>
@@ -15596,7 +15566,7 @@
         <v>24</v>
       </c>
       <c r="I121" s="56" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="J121" s="57">
         <v>45000</v>
@@ -15608,10 +15578,10 @@
         <v>138</v>
       </c>
       <c r="M121" s="56" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="O121" s="56">
         <v>62</v>
@@ -15635,10 +15605,10 @@
         <v>138</v>
       </c>
       <c r="V121" s="56" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="W121" s="56" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="X121" s="56" t="s">
         <v>42</v>
@@ -15649,7 +15619,7 @@
         <v>46092</v>
       </c>
       <c r="B122" s="47" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C122" s="44" t="s">
         <v>47</v>
@@ -15670,7 +15640,7 @@
         <v>17</v>
       </c>
       <c r="I122" s="56" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="J122" s="57">
         <v>56000</v>
@@ -15682,10 +15652,10 @@
         <v>138</v>
       </c>
       <c r="M122" s="56" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="O122" s="56" t="s">
         <v>138</v>
@@ -15712,7 +15682,7 @@
         <v>138</v>
       </c>
       <c r="W122" s="56" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="X122" s="56" t="s">
         <v>42</v>
@@ -17181,7 +17151,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -17207,46 +17177,46 @@
         <v>85</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="40" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>97</v>
       </c>
       <c r="O2" s="41" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -17254,7 +17224,7 @@
         <v>46087</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="2" t="s">
@@ -17264,34 +17234,34 @@
         <v>39900</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G3" s="26">
         <v>12</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N3" s="26" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P3" s="30"/>
     </row>
@@ -17300,7 +17270,7 @@
         <v>46087</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="27" t="s">
@@ -17310,7 +17280,7 @@
         <v>53900</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="G4" s="15">
         <v>2</v>
@@ -17319,25 +17289,25 @@
         <v>60</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P4" s="30"/>
     </row>
@@ -17346,7 +17316,7 @@
         <v>46087</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="27" t="s">
@@ -17358,28 +17328,28 @@
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P5" s="30"/>
     </row>
@@ -17388,7 +17358,7 @@
         <v>46087</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="27" t="s">
@@ -17398,7 +17368,7 @@
         <v>45990</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="G6" s="15">
         <v>1</v>
@@ -17407,25 +17377,25 @@
         <v>50</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P6" s="30"/>
     </row>
@@ -17434,7 +17404,7 @@
         <v>46087</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="27" t="s">
@@ -17444,7 +17414,7 @@
         <v>52990</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G7" s="15">
         <v>1</v>
@@ -17453,21 +17423,21 @@
         <v>65</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P7" s="30"/>
     </row>
@@ -17476,7 +17446,7 @@
         <v>46087</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="27" t="s">
@@ -17486,30 +17456,30 @@
         <v>69990</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="G8" s="15">
         <v>1</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P8" s="30"/>
     </row>
@@ -17518,7 +17488,7 @@
         <v>46087</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="27" t="s">
@@ -17528,7 +17498,7 @@
         <v>47900</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="G9" s="15">
         <v>3</v>
@@ -17537,25 +17507,25 @@
         <v>40</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="O9" s="33" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P9" s="30"/>
     </row>
@@ -17564,10 +17534,10 @@
         <v>46087</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>14</v>
@@ -17576,10 +17546,10 @@
         <v>53900</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H10" s="15">
         <v>65</v>
@@ -17588,17 +17558,17 @@
         <v>10</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="O10" s="33"/>
       <c r="P10" s="30"/>
@@ -17608,10 +17578,10 @@
         <v>46087</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="20">
@@ -17623,20 +17593,20 @@
         <v>60</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="33"/>
       <c r="P11" s="30" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -17644,41 +17614,41 @@
         <v>46087</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="20">
         <v>54990</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G12" s="15">
         <v>2</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="O12" s="33"/>
       <c r="P12" s="30" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -17686,41 +17656,41 @@
         <v>46087</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="20">
         <v>64990</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G13" s="15">
         <v>2</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O13" s="33"/>
       <c r="P13" s="30" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -17728,10 +17698,10 @@
         <v>46090</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>14</v>
@@ -17740,10 +17710,10 @@
         <v>56900</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H14" s="15">
         <v>75</v>
@@ -17752,22 +17722,22 @@
         <v>20</v>
       </c>
       <c r="J14" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="O14" s="33" t="s">
         <v>314</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="O14" s="33" t="s">
-        <v>324</v>
       </c>
       <c r="P14" s="30"/>
     </row>
@@ -17776,10 +17746,10 @@
         <v>46090</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>14</v>
@@ -17788,10 +17758,10 @@
         <v>65900</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
@@ -17800,22 +17770,22 @@
         <v>20</v>
       </c>
       <c r="J15" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="O15" s="33" t="s">
         <v>314</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="N15" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="O15" s="33" t="s">
-        <v>324</v>
       </c>
       <c r="P15" s="30"/>
     </row>
@@ -17824,10 +17794,10 @@
         <v>46090</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>14</v>
@@ -17836,10 +17806,10 @@
         <v>75900</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H16" s="26">
         <v>130</v>
@@ -17848,22 +17818,22 @@
         <v>25</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="O16" s="34" t="s">
         <v>314</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="O16" s="34" t="s">
-        <v>324</v>
       </c>
       <c r="P16" s="31"/>
     </row>
@@ -17872,10 +17842,10 @@
         <v>46090</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>14</v>
@@ -17884,32 +17854,32 @@
         <v>99900</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="O17" s="34" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P17" s="31"/>
     </row>
@@ -17918,10 +17888,10 @@
         <v>46090</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>14</v>
@@ -17930,10 +17900,10 @@
         <v>62900</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H18" s="26">
         <v>60</v>
@@ -17942,22 +17912,22 @@
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="O18" s="34" t="s">
         <v>323</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="O18" s="34" t="s">
-        <v>333</v>
       </c>
       <c r="P18" s="31"/>
     </row>
@@ -17966,10 +17936,10 @@
         <v>46090</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>14</v>
@@ -17978,10 +17948,10 @@
         <v>83900</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H19" s="26">
         <v>140</v>
@@ -17990,22 +17960,22 @@
         <v>25</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="O19" s="34" t="s">
         <v>323</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="O19" s="34" t="s">
-        <v>333</v>
       </c>
       <c r="P19" s="31"/>
     </row>
@@ -18014,10 +17984,10 @@
         <v>46090</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D20" s="27" t="s">
         <v>14</v>
@@ -18026,10 +17996,10 @@
         <v>104900</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H20" s="26">
         <v>180</v>
@@ -18038,22 +18008,22 @@
         <v>50</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="O20" s="34" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P20" s="31"/>
     </row>
@@ -18062,10 +18032,10 @@
         <v>46090</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>14</v>
@@ -18074,32 +18044,32 @@
         <v>128900</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O21" s="34" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P21" s="31"/>
     </row>
@@ -18108,10 +18078,10 @@
         <v>46090</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D22" s="27" t="s">
         <v>14</v>
@@ -18120,10 +18090,10 @@
         <v>93900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H22" s="26">
         <v>60</v>
@@ -18132,22 +18102,22 @@
         <v>50</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O22" s="34" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="P22" s="31"/>
     </row>
@@ -18156,10 +18126,10 @@
         <v>46090</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>14</v>
@@ -18168,10 +18138,10 @@
         <v>60900</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H23" s="26">
         <v>55</v>
@@ -18180,20 +18150,20 @@
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L23" s="26"/>
       <c r="M23" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O23" s="32" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="P23" s="31"/>
     </row>
@@ -18202,10 +18172,10 @@
         <v>46090</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D24" s="27" t="s">
         <v>14</v>
@@ -18214,10 +18184,10 @@
         <v>75900</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H24" s="26">
         <v>100</v>
@@ -18226,25 +18196,25 @@
         <v>25</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M24" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="O24" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="O24" s="34" t="s">
-        <v>333</v>
-      </c>
       <c r="P24" s="30" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="105" x14ac:dyDescent="0.25">
@@ -18252,10 +18222,10 @@
         <v>46090</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>14</v>
@@ -18264,10 +18234,10 @@
         <v>86900</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="H25" s="26">
         <v>105</v>
@@ -18276,25 +18246,25 @@
         <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -18302,10 +18272,10 @@
         <v>46090</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D26" s="27" t="s">
         <v>14</v>
@@ -18322,21 +18292,21 @@
         <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L26" s="26"/>
       <c r="M26" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="O26" s="32"/>
       <c r="P26" s="30" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18344,10 +18314,10 @@
         <v>46090</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D27" s="27" t="s">
         <v>14</v>
@@ -18364,21 +18334,21 @@
         <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O27" s="32"/>
       <c r="P27" s="30" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18386,10 +18356,10 @@
         <v>46090</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>14</v>
@@ -18406,21 +18376,21 @@
         <v>20</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L28" s="26"/>
       <c r="M28" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="O28" s="32"/>
       <c r="P28" s="30" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18428,10 +18398,10 @@
         <v>46090</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>14</v>
@@ -18448,21 +18418,21 @@
         <v>10</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L29" s="26"/>
       <c r="M29" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O29" s="32"/>
       <c r="P29" s="31" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -18470,10 +18440,10 @@
         <v>46090</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>14</v>
@@ -18482,10 +18452,10 @@
         <v>38900</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="H30" s="26">
         <v>47</v>
@@ -18494,21 +18464,21 @@
         <v>5</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L30" s="26"/>
       <c r="M30" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O30" s="32"/>
       <c r="P30" s="30" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -18936,7 +18906,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -18962,37 +18932,37 @@
         <v>0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -19000,7 +18970,7 @@
         <v>46088</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -19019,19 +18989,19 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N3" s="14"/>
     </row>
@@ -19040,7 +19010,7 @@
         <v>46088</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -19058,22 +19028,22 @@
         <v>7</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N4" s="2"/>
     </row>
@@ -19082,7 +19052,7 @@
         <v>46088</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -19101,19 +19071,19 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -19122,7 +19092,7 @@
         <v>46088</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -19141,19 +19111,19 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N6" s="2"/>
     </row>
@@ -19162,7 +19132,7 @@
         <v>46088</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
@@ -19181,19 +19151,19 @@
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N7" s="2"/>
     </row>
@@ -19202,7 +19172,7 @@
         <v>46088</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
@@ -19221,19 +19191,19 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N8" s="2"/>
     </row>
@@ -19242,7 +19212,7 @@
         <v>46088</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -19261,19 +19231,19 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N9" s="2"/>
     </row>
@@ -19282,7 +19252,7 @@
         <v>46088</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -19301,19 +19271,19 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N10" s="2"/>
     </row>
@@ -19322,7 +19292,7 @@
         <v>46088</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>14</v>
@@ -19341,19 +19311,19 @@
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N11" s="2"/>
     </row>
@@ -19362,7 +19332,7 @@
         <v>46088</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
@@ -19380,22 +19350,22 @@
         <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N12" s="2"/>
     </row>
@@ -19404,7 +19374,7 @@
         <v>46088</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>14</v>
@@ -19423,19 +19393,19 @@
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N13" s="2"/>
     </row>
@@ -19444,7 +19414,7 @@
         <v>46088</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>14</v>
@@ -19463,19 +19433,19 @@
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N14" s="2"/>
     </row>
@@ -19484,7 +19454,7 @@
         <v>46088</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -19503,19 +19473,19 @@
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N15" s="2"/>
     </row>
@@ -19524,7 +19494,7 @@
         <v>46088</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>22</v>
@@ -19543,19 +19513,19 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N16" s="2"/>
     </row>
@@ -19564,7 +19534,7 @@
         <v>46088</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
@@ -19583,19 +19553,19 @@
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -19604,7 +19574,7 @@
         <v>46088</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>22</v>
@@ -19623,19 +19593,19 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N18" s="2"/>
     </row>
@@ -19644,7 +19614,7 @@
         <v>46088</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>22</v>
@@ -19663,19 +19633,19 @@
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N19" s="2"/>
     </row>
@@ -19684,7 +19654,7 @@
         <v>46088</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
@@ -19703,19 +19673,19 @@
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N20" s="2"/>
     </row>
@@ -19724,7 +19694,7 @@
         <v>46088</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>22</v>
@@ -19743,19 +19713,19 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -19764,7 +19734,7 @@
         <v>46088</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>22</v>
@@ -19783,19 +19753,19 @@
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N22" s="2"/>
     </row>
@@ -19804,7 +19774,7 @@
         <v>46088</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>22</v>
@@ -19820,22 +19790,22 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N23" s="2"/>
     </row>
@@ -19844,7 +19814,7 @@
         <v>46088</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
@@ -19863,19 +19833,19 @@
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -19884,7 +19854,7 @@
         <v>46088</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>30</v>
@@ -19903,19 +19873,19 @@
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -19924,7 +19894,7 @@
         <v>46088</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>30</v>
@@ -19943,19 +19913,19 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -19964,7 +19934,7 @@
         <v>46088</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
@@ -19983,19 +19953,19 @@
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -20004,7 +19974,7 @@
         <v>46088</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>30</v>
@@ -20023,19 +19993,19 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -20044,7 +20014,7 @@
         <v>46088</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>30</v>
@@ -20063,19 +20033,19 @@
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -20084,7 +20054,7 @@
         <v>46088</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>30</v>
@@ -20102,22 +20072,22 @@
         <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -20126,7 +20096,7 @@
         <v>46088</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>30</v>
@@ -20145,19 +20115,19 @@
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N31" s="2"/>
     </row>
@@ -20166,7 +20136,7 @@
         <v>46088</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>30</v>
@@ -20185,19 +20155,19 @@
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -20206,7 +20176,7 @@
         <v>46088</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>30</v>
@@ -20225,19 +20195,19 @@
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -20246,7 +20216,7 @@
         <v>46088</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>30</v>
@@ -20265,19 +20235,19 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -20286,7 +20256,7 @@
         <v>46088</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>30</v>
@@ -20305,19 +20275,19 @@
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -20326,7 +20296,7 @@
         <v>46088</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>39</v>
@@ -20345,19 +20315,19 @@
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N36" s="2"/>
     </row>
@@ -20366,7 +20336,7 @@
         <v>46088</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>39</v>
@@ -20385,19 +20355,19 @@
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -20406,7 +20376,7 @@
         <v>46088</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>39</v>
@@ -20425,19 +20395,19 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -20446,7 +20416,7 @@
         <v>46088</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>39</v>
@@ -20465,19 +20435,19 @@
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="M39" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -20486,7 +20456,7 @@
         <v>46088</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>39</v>
@@ -20505,19 +20475,19 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M40" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -20526,7 +20496,7 @@
         <v>46088</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>39</v>
@@ -20545,19 +20515,19 @@
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N41" s="2"/>
     </row>
@@ -20566,7 +20536,7 @@
         <v>46088</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>39</v>
@@ -20585,19 +20555,19 @@
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -20606,7 +20576,7 @@
         <v>46088</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
@@ -20625,19 +20595,19 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N43" s="2"/>
     </row>
@@ -20646,7 +20616,7 @@
         <v>46088</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>39</v>
@@ -20665,19 +20635,19 @@
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N44" s="2"/>
     </row>
@@ -20686,7 +20656,7 @@
         <v>46088</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>39</v>
@@ -20705,19 +20675,19 @@
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N45" s="2"/>
     </row>
@@ -20726,7 +20696,7 @@
         <v>46088</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>39</v>
@@ -20745,19 +20715,19 @@
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N46" s="2"/>
     </row>
@@ -20766,7 +20736,7 @@
         <v>46088</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>39</v>
@@ -20785,19 +20755,19 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N47" s="2"/>
     </row>
@@ -20806,7 +20776,7 @@
         <v>46088</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>45</v>
@@ -20825,19 +20795,19 @@
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M48" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N48" s="2"/>
     </row>
@@ -20846,7 +20816,7 @@
         <v>46088</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>45</v>
@@ -20865,19 +20835,19 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N49" s="2"/>
     </row>
@@ -20886,7 +20856,7 @@
         <v>46088</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>45</v>
@@ -20905,19 +20875,19 @@
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N50" s="2"/>
     </row>
@@ -20926,7 +20896,7 @@
         <v>46088</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>45</v>
@@ -20945,19 +20915,19 @@
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N51" s="2"/>
     </row>
@@ -20966,7 +20936,7 @@
         <v>46088</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>45</v>
@@ -20985,19 +20955,19 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N52" s="2"/>
     </row>
@@ -21006,7 +20976,7 @@
         <v>46088</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>45</v>
@@ -21025,19 +20995,19 @@
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N53" s="2"/>
     </row>
@@ -21046,7 +21016,7 @@
         <v>46088</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>45</v>
@@ -21065,19 +21035,19 @@
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N54" s="2"/>
     </row>
@@ -21086,7 +21056,7 @@
         <v>46088</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>45</v>
@@ -21105,19 +21075,19 @@
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N55" s="2"/>
     </row>
@@ -21126,7 +21096,7 @@
         <v>46088</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>45</v>
@@ -21145,19 +21115,19 @@
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N56" s="2"/>
     </row>
@@ -21166,7 +21136,7 @@
         <v>46088</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>45</v>
@@ -21185,19 +21155,19 @@
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N57" s="2"/>
     </row>
@@ -21206,7 +21176,7 @@
         <v>46090</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>14</v>
@@ -21218,27 +21188,27 @@
         <v>5000</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="G58" s="15">
         <v>3</v>
       </c>
       <c r="H58" s="15"/>
       <c r="I58" s="15" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M58" s="15"/>
       <c r="N58" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21246,7 +21216,7 @@
         <v>46090</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>14</v>
@@ -21258,27 +21228,27 @@
         <v>8000</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="G59" s="15">
         <v>6</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M59" s="15"/>
       <c r="N59" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21286,7 +21256,7 @@
         <v>46090</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>14</v>
@@ -21298,27 +21268,27 @@
         <v>9000</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="G60" s="15">
         <v>7</v>
       </c>
       <c r="H60" s="15"/>
       <c r="I60" s="15" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L60" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M60" s="15"/>
       <c r="N60" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21326,7 +21296,7 @@
         <v>46090</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>14</v>
@@ -21338,27 +21308,27 @@
         <v>13000</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="G61" s="15">
         <v>10</v>
       </c>
       <c r="H61" s="15"/>
       <c r="I61" s="15" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M61" s="15"/>
       <c r="N61" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21366,7 +21336,7 @@
         <v>46090</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>14</v>
@@ -21378,27 +21348,27 @@
         <v>23000</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="G62" s="15">
         <v>20</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="15" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M62" s="15"/>
       <c r="N62" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21406,7 +21376,7 @@
         <v>46090</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>14</v>
@@ -21418,27 +21388,27 @@
         <v>33000</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="G63" s="15">
         <v>30</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="15" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M63" s="15"/>
       <c r="N63" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21446,7 +21416,7 @@
         <v>46090</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>14</v>
@@ -21458,27 +21428,27 @@
         <v>43000</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="G64" s="15">
         <v>30</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="15" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M64" s="15"/>
       <c r="N64" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -21486,7 +21456,7 @@
         <v>46090</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>14</v>
@@ -21498,27 +21468,27 @@
         <v>100000</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="G65" s="15">
         <v>30</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="15" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M65" s="15"/>
       <c r="N65" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21526,7 +21496,7 @@
         <v>46090</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>14</v>
@@ -21538,25 +21508,25 @@
         <v>13000</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="G66" s="15">
         <v>7</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K66" s="15"/>
       <c r="L66" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M66" s="15"/>
       <c r="N66" s="15" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21564,7 +21534,7 @@
         <v>46090</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>14</v>
@@ -21576,25 +21546,25 @@
         <v>23000</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="G67" s="15">
         <v>15</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K67" s="15"/>
       <c r="L67" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M67" s="15"/>
       <c r="N67" s="15" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21602,7 +21572,7 @@
         <v>46090</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>14</v>
@@ -21614,25 +21584,25 @@
         <v>33000</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="G68" s="15">
         <v>30</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K68" s="15"/>
       <c r="L68" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M68" s="15"/>
       <c r="N68" s="15" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -21640,7 +21610,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>14</v>
@@ -21652,27 +21622,27 @@
         <v>4500</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="G69" s="15">
         <v>7</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="15" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M69" s="15"/>
       <c r="N69" s="15" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -21835,29 +21805,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008132F03F7BAE544691E1D8ED0BBAB87D" ma:contentTypeVersion="21" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e484fd9c9d78115df5d140a0e15bddb5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="612f0692-a35d-4227-ae2b-09b69c7561dc" xmlns:ns3="c9fa2ff5-4241-4755-bdec-11c5f369898d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60915895e4af9a5e40828d772a1103ab" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -22135,27 +22082,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
-    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B03BB360-2000-407D-9849-F3FC94EAD1FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22173,4 +22123,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
+    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/Benchmarking.xlsx
+++ b/assets/Benchmarking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO NO BORRAR\Documents\GitHub\asesores\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95CBFE-FC47-4168-9216-FF421C82A6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D584CE-E5F0-4267-AA44-79CF762A839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F3156A63-ABA6-4DCB-AB8A-B4C8C83E2F35}"/>
   </bookViews>
@@ -42,160 +42,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="14">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="23"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="33"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="47"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="57"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="69"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="80"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="90"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="98"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="106"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="116"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="123"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="133"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="14">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-    <bk>
-      <rc t="1" v="6"/>
-    </bk>
-    <bk>
-      <rc t="1" v="7"/>
-    </bk>
-    <bk>
-      <rc t="1" v="8"/>
-    </bk>
-    <bk>
-      <rc t="1" v="9"/>
-    </bk>
-    <bk>
-      <rc t="1" v="10"/>
-    </bk>
-    <bk>
-      <rc t="1" v="11"/>
-    </bk>
-    <bk>
-      <rc t="1" v="12"/>
-    </bk>
-    <bk>
-      <rc t="1" v="13"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3204" uniqueCount="468">
   <si>
     <t>Operador</t>
   </si>
@@ -1585,6 +1433,21 @@
   </si>
   <si>
     <t>OTTs Incluidas Nombre de la OTT (En caso que aplique, de no ser asi, poner N/A)</t>
+  </si>
+  <si>
+    <t>Itagüí</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>Medellín</t>
+  </si>
+  <si>
+    <t>Calarcá</t>
+  </si>
+  <si>
+    <t>La Tebaida</t>
   </si>
 </sst>
 </file>
@@ -3937,2240 +3800,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-  <types>
-    <type name="_linkedentity2">
-      <keyFlags>
-        <key name="%EntityServiceId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityCulture">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%cvi">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-      </keyFlags>
-    </type>
-    <type name="_linkedentity2core">
-      <keyFlags>
-        <key name="%EntityServiceId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityCulture">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%IsRefreshable">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-        <key name="%ProviderInfo">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataProviderExternalLinkLogo">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataProviderExternalLink">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataRetrievedTime">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-        <key name="%EntityDomainIdString">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%InfoToolTipLabelNames">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%InfoToolTipLabelValues">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%InfoToolTipLabelValuesType">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataProviderString">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%ClassificationId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%OutdatedReason">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-      </keyFlags>
-    </type>
-    <type name="_webimage">
-      <keyFlags>
-        <key name="WebImageIdentifier">
-          <flag name="ShowInCardView" value="0"/>
-        </key>
-      </keyFlags>
-    </type>
-  </types>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdRichValueWebImage.xml><?xml version="1.0" encoding="utf-8"?>
-<webImagesSrd xmlns="http://schemas.microsoft.com/office/spreadsheetml/2020/richdatawebimage" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <webImageSrd>
-    <address r:id="rId1"/>
-    <moreImagesAddress r:id="rId2"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId3"/>
-    <moreImagesAddress r:id="rId4"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId5"/>
-    <moreImagesAddress r:id="rId6"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId7"/>
-    <moreImagesAddress r:id="rId8"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId9"/>
-    <moreImagesAddress r:id="rId10"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId11"/>
-    <moreImagesAddress r:id="rId12"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId13"/>
-    <moreImagesAddress r:id="rId14"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId15"/>
-    <moreImagesAddress r:id="rId16"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId17"/>
-    <moreImagesAddress r:id="rId18"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId19"/>
-    <moreImagesAddress r:id="rId20"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId21"/>
-    <moreImagesAddress r:id="rId22"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId23"/>
-    <moreImagesAddress r:id="rId24"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId25"/>
-    <moreImagesAddress r:id="rId26"/>
-  </webImageSrd>
-  <webImageSrd>
-    <address r:id="rId27"/>
-    <moreImagesAddress r:id="rId28"/>
-  </webImageSrd>
-</webImagesSrd>
-</file>
-
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="13">
-  <a r="1">
-    <v t="r">6</v>
-  </a>
-  <a r="1">
-    <v t="r">17</v>
-  </a>
-  <a r="1">
-    <v t="s">UTC-05:00</v>
-  </a>
-  <a r="1">
-    <v t="r">28</v>
-  </a>
-  <a r="1">
-    <v t="r">40</v>
-  </a>
-  <a r="1">
-    <v t="s">Hora estándar del centro</v>
-  </a>
-  <a r="1">
-    <v t="r">52</v>
-  </a>
-  <a r="1">
-    <v t="r">63</v>
-  </a>
-  <a r="1">
-    <v t="s">Horario del este de América del Norte</v>
-  </a>
-  <a r="1">
-    <v t="r">75</v>
-  </a>
-  <a r="1">
-    <v t="r">85</v>
-  </a>
-  <a r="1">
-    <v t="r">111</v>
-  </a>
-  <a r="1">
-    <v t="r">128</v>
-  </a>
-</arrayData>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="141">
-  <rv s="0">
-    <v>536870912</v>
-    <v>Itagüí</v>
-    <v>a0741dfb-e4f1-1104-00a6-0f7afedb438a</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>21.09</fb>
-    <v>9</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Antioquia</v>
-    <v>d3614470-a93c-5d64-a636-9da2dff33c3d</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>0</v>
-    <v>7</v>
-    <v>0</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Itagüí</v>
-  </rv>
-  <rv s="1">
-    <fb>6.1726000000000001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Itag%c3%bc%c3%ad&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>León Mario Bedoya López (Alcalde)</v>
-    <v>902b018f-53fb-a38e-31e3-a75f31975be5</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.6096</fb>
-    <v>10</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Colombia</v>
-    <v>c396e3d8-2a85-d230-f691-7850536d840e</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>276744</fb>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>a0741dfb-e4f1-1104-00a6-0f7afedb438a</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>1</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Itagüí</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>1</v>
-    <v>Itagüí es un municipio colombiano ubicado en el sur del Valle de Aburrá en el departamento de Antioquia. Este forma parte de la denominada Área metropolitana del Valle de Aburrá y está conurbado con la ciudad de Medellín. Limita por el este con ...</v>
-    <v>2</v>
-    <v>3</v>
-    <v>4</v>
-    <v>5</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Itagüí</v>
-    <v>9</v>
-    <v>10</v>
-    <v>Itagüí</v>
-    <v>mdp/vdpid/5577501387832426498</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Envigado</v>
-    <v>9a33e68b-f071-4759-9d54-1b7673a98c97</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>78.78</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>1</v>
-    <v>7</v>
-    <v>11</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Envigado</v>
-  </rv>
-  <rv s="1">
-    <fb>6.1719444444444003</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Envigado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Braulio Espinosa (Alcalde)</v>
-    <v>dfcd7883-acba-4372-e0e3-4165a68f6ba8</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.580277777777994</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>228848</fb>
-    <v>9</v>
-  </rv>
-  <rv s="4">
-    <v>2</v>
-  </rv>
-  <rv s="6">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>9a33e68b-f071-4759-9d54-1b7673a98c97</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>12</v>
-    <v>2</v>
-    <v>13</v>
-    <v>Envigado</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>13</v>
-    <v>Envigado es un municipio de Colombia ubicado en el sur del valle de Aburrá del departamento de Antioquia. Limita por el norte con el distrito de Medellín, por el este con los municipios de Rionegro y El Retiro, por el sur con los municipios de ...</v>
-    <v>2</v>
-    <v>14</v>
-    <v>15</v>
-    <v>16</v>
-    <v>18</v>
-    <v>19</v>
-    <v>Envigado</v>
-    <v>9</v>
-    <v>20</v>
-    <v>Envigado</v>
-    <v>mdp/vdpid/5577507221069103107</v>
-    <v>21</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Sabaneta</v>
-    <v>2ceaae1d-199a-38ad-e392-8be7fa95d025</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>15</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>2</v>
-    <v>7</v>
-    <v>14</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Sabaneta</v>
-  </rv>
-  <rv s="1">
-    <fb>6.1508333333333001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Sabaneta+Colombia&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Santiago Montoya (Alcalde)</v>
-    <v>ebcfaa84-65b0-eef8-781f-e863c34a9395</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.614999999999995</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>82375</fb>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>2ceaae1d-199a-38ad-e392-8be7fa95d025</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>15</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Sabaneta</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>24</v>
-    <v>Sabaneta es un municipio colombiano ubicado en el Valle de Aburrá en el departamento de Antioquia. Limita por el norte con el municipio de Itagüí, por el este con Envigado, por el sur con Caldas, y por el oeste La Estrella.</v>
-    <v>2</v>
-    <v>25</v>
-    <v>26</v>
-    <v>27</v>
-    <v>29</v>
-    <v>30</v>
-    <v>Sabaneta</v>
-    <v>9</v>
-    <v>31</v>
-    <v>Sabaneta</v>
-    <v>mdp/vdpid/5577501419205820419</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Antonio</v>
-    <v>227b2515-cb4d-49b7-9e37-9f46f910612e</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1208.7773360000001</fb>
-    <v>9</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Texas</v>
-    <v>00a23ccd-3344-461c-8b9f-c2bb55be5815</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Condado de Béxar</v>
-    <v>02b1f4e0-5e72-6d90-157d-2e78b76f3dd3</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>3</v>
-    <v>7</v>
-    <v>16</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of San Antonio</v>
-  </rv>
-  <rv s="1">
-    <fb>29.425000000000001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=San+Antonio+Texas&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Ron Nirenberg (Alcalde)</v>
-    <v>52c0337f-1265-eed4-b39c-1061826f5ca5</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>4</v>
-  </rv>
-  <rv s="1">
-    <fb>-98.493888888888904</fb>
-    <v>10</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Estados Unidos</v>
-    <v>5232ed96-85b1-2edb-12c6-63e6c597a1de</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1434625</fb>
-    <v>9</v>
-  </rv>
-  <rv s="4">
-    <v>5</v>
-  </rv>
-  <rv s="7">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>227b2515-cb4d-49b7-9e37-9f46f910612e</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>17</v>
-    <v>18</v>
-    <v>19</v>
-    <v>San Antonio</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>20</v>
-    <v>34</v>
-    <v>San Antonio es una ciudad ubicada en el condado de Béxar, en el estado estadounidense de Texas. En el Censo de 2010 tenía una población de 1 327 407 habitantes y una densidad poblacional de 1098,14 personas por km². Está atravesada por el río ...</v>
-    <v>35</v>
-    <v>36</v>
-    <v>37</v>
-    <v>38</v>
-    <v>39</v>
-    <v>41</v>
-    <v>42</v>
-    <v>San Antonio</v>
-    <v>43</v>
-    <v>44</v>
-    <v>San Antonio</v>
-    <v>mdp/vdpid/5108677976363368450</v>
-    <v>45</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Medellín</v>
-    <v>7b1377e4-8d6a-bcd0-6cb4-7b7c0a8f94b5</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>380.74</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>7</v>
-    <v>21</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Medellín</v>
-  </rv>
-  <rv s="1">
-    <fb>6.2447472222222</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Medell%c3%adn&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Fico Gutierrez (Alcalde)</v>
-    <v>882f5921-5342-f5f7-cffb-aefbd18d4874</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>6</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.574827777777998</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>2529403</fb>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>7b1377e4-8d6a-bcd0-6cb4-7b7c0a8f94b5</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>22</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Medellín</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>48</v>
-    <v>Medellín, es un distrito de Colombia y capital del departamento de Antioquia. Es la ciudad más poblada del departamento y la segunda más poblada del país después de Bogotá. Está ubicada en la parte más ancha de la región natural conocida como ...</v>
-    <v>2</v>
-    <v>49</v>
-    <v>50</v>
-    <v>51</v>
-    <v>53</v>
-    <v>54</v>
-    <v>Medellín</v>
-    <v>9</v>
-    <v>55</v>
-    <v>Medellín</v>
-    <v>mdp/vdpid/5577506192692871181</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Pereira</v>
-    <v>d348f442-8e77-a0fc-3525-8c1a05184766</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>702</fb>
-    <v>9</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Risaralda</v>
-    <v>12859881-10e7-a44f-aa52-ed6ecbc80e7c</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>5</v>
-    <v>7</v>
-    <v>23</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Pereira</v>
-  </rv>
-  <rv s="1">
-    <fb>4.8142777777778001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Pereira&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Mauricio Salazar Peláez (Alcalde)</v>
-    <v>75ca89fe-0115-3508-eb3b-797a07abc107</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>7</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.694558333333006</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>481768</fb>
-    <v>9</v>
-  </rv>
-  <rv s="4">
-    <v>8</v>
-  </rv>
-  <rv s="6">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>d348f442-8e77-a0fc-3525-8c1a05184766</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>24</v>
-    <v>2</v>
-    <v>13</v>
-    <v>Pereira</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>25</v>
-    <v>58</v>
-    <v>Pereira es un municipio colombiano, capital del departamento de Risaralda. Es la ciudad más poblada de la región del eje cafetero; integra el Área Metropolitana de Centro Occidente junto con los municipios de Dosquebradas y La Virginia. Está ...</v>
-    <v>59</v>
-    <v>60</v>
-    <v>61</v>
-    <v>62</v>
-    <v>64</v>
-    <v>65</v>
-    <v>Pereira</v>
-    <v>9</v>
-    <v>66</v>
-    <v>Pereira</v>
-    <v>mdp/vdpid/5580596817134878721</v>
-    <v>67</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Armenia</v>
-    <v>9f713bea-584e-bcb2-fad2-76734e840ef6</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>140</fb>
-    <v>9</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Quindío</v>
-    <v>0bb62acd-b714-a5dd-dc49-6f69ddaba02c</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>6</v>
-    <v>7</v>
-    <v>26</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Armenia</v>
-  </rv>
-  <rv s="1">
-    <fb>4.5388888888889003</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Armenia+Quind%c3%ado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>José Manuel Ríos Morales (Alcalde)</v>
-    <v>e6a33032-bef6-fa3d-0515-57afb7af841b</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>9</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.672499999999999</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>304314</fb>
-    <v>9</v>
-  </rv>
-  <rv s="6">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>9f713bea-584e-bcb2-fad2-76734e840ef6</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>27</v>
-    <v>2</v>
-    <v>13</v>
-    <v>Armenia</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>70</v>
-    <v>Armenia es un municipio colombiano, capital del departamento del Quindío y núcleo económico de su área metropolitana. Es una de las principales ciudades del Eje Cafetero Colombiano, la Región Paisa y el Paisaje Cultural Cafetero. Fue fundada por ...</v>
-    <v>71</v>
-    <v>72</v>
-    <v>73</v>
-    <v>74</v>
-    <v>76</v>
-    <v>77</v>
-    <v>Armenia</v>
-    <v>9</v>
-    <v>78</v>
-    <v>Armenia</v>
-    <v>mdp/vdpid/5580601899104600065</v>
-    <v>21</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Calarcá</v>
-    <v>dda927e3-faeb-50d3-05dc-d6f742be400e</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>219.23</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>7</v>
-    <v>7</v>
-    <v>28</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Calarcá</v>
-  </rv>
-  <rv s="1">
-    <fb>4.5291666666666996</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Calarc%c3%a1+Quind%c3%ado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Luis Alberto Balsero Contreras (Alcalde)</v>
-    <v>3692cbd1-00a8-e7d6-6d34-ff30cc35d436</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.640833333333006</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>75979</fb>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>dda927e3-faeb-50d3-05dc-d6f742be400e</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>29</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Calarcá</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>25</v>
-    <v>81</v>
-    <v>Calarcá es un municipio colombiano perteneciente al departamento del Quindío. Es el segundo municipio con mayor cantidad de habitantes del departamento, después de la capital: Armenia. La ciudad es gobernada por un Alcalde y un Concejo ...</v>
-    <v>71</v>
-    <v>82</v>
-    <v>83</v>
-    <v>84</v>
-    <v>86</v>
-    <v>87</v>
-    <v>Calarcá</v>
-    <v>9</v>
-    <v>88</v>
-    <v>Calarcá</v>
-    <v>mdp/vdpid/5580613724273639425</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Montenegro</v>
-    <v>21890e6d-913d-80e6-cc2f-910169b1564c</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>149</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>8</v>
-    <v>7</v>
-    <v>30</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Montenegro</v>
-  </rv>
-  <rv s="1">
-    <fb>4.5652777777778004</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Montenegro+Quind%c3%ado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.751111111111001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>41996</fb>
-    <v>9</v>
-  </rv>
-  <rv s="8">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>21890e6d-913d-80e6-cc2f-910169b1564c</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>32</v>
-    <v>2</v>
-    <v>33</v>
-    <v>Montenegro</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>20</v>
-    <v>91</v>
-    <v>Montenegro es un municipio del departamento del Quindío en Colombia. Su cabecera municipal se localiza a los 4° 34 de latitud Norte, y 75° 45 de longitud al oeste de Greenwich y se sitúa a 10 kilómetros al oeste de Armenia haciendo parte de su ...</v>
-    <v>71</v>
-    <v>92</v>
-    <v>93</v>
-    <v>94</v>
-    <v>95</v>
-    <v>Montenegro</v>
-    <v>9</v>
-    <v>96</v>
-    <v>Montenegro</v>
-    <v>mdp/vdpid/5580613073820975105</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Circasia</v>
-    <v>1bcdad08-78a6-2899-aea2-727fccbe0b10</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>91</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>9</v>
-    <v>7</v>
-    <v>34</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Circasia</v>
-  </rv>
-  <rv s="1">
-    <fb>4.62</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Circasia+Quind%c3%ado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.634722222222194</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>28162</fb>
-    <v>9</v>
-  </rv>
-  <rv s="8">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>1bcdad08-78a6-2899-aea2-727fccbe0b10</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>35</v>
-    <v>2</v>
-    <v>33</v>
-    <v>Circasia</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>99</v>
-    <v>Circasia es un municipio ubicado en el norte del departamento del Quindío, Colombia. Está localizado a 7 km al norte de la capital del departamento, Armenia, hace parte del área metropolitana de la misma.</v>
-    <v>71</v>
-    <v>100</v>
-    <v>101</v>
-    <v>102</v>
-    <v>103</v>
-    <v>Circasia</v>
-    <v>9</v>
-    <v>104</v>
-    <v>Circasia</v>
-    <v>mdp/vdpid/5580601732875943937</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>La Tebaida</v>
-    <v>818b56be-0dae-0d6d-3dce-e47209c46395</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>89</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>10</v>
-    <v>7</v>
-    <v>36</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of La Tebaida</v>
-  </rv>
-  <rv s="1">
-    <fb>4.4522222222221997</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=La+Tebaida+Colombia&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Rosa Patricia Buitrago Giraldo (Alcalde)</v>
-    <v>2bab4973-a8bd-4f58-1376-4fe1cba182ef</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.786666666667003</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>42163</fb>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>818b56be-0dae-0d6d-3dce-e47209c46395</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>38</v>
-    <v>2</v>
-    <v>3</v>
-    <v>La Tebaida</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>39</v>
-    <v>107</v>
-    <v>La Tebaida es un municipio del departamento de Quindío en Colombia. Según el censo de 2005, tiene 32 748 habitantes, de los cuales 27 000 habitan en la zona urbana. La Zona Franca del Quindío y el Aeropuerto Internacional El Edén, que se ubican ...</v>
-    <v>71</v>
-    <v>108</v>
-    <v>109</v>
-    <v>110</v>
-    <v>112</v>
-    <v>113</v>
-    <v>La Tebaida</v>
-    <v>9</v>
-    <v>114</v>
-    <v>La Tebaida</v>
-    <v>mdp/vdpid/5580612693783478273</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Quimbaya</v>
-    <v>e11d34ac-06ec-fddd-2922-bcc1256911ae</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>11</v>
-    <v>7</v>
-    <v>40</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Quimbaya</v>
-  </rv>
-  <rv s="1">
-    <fb>4.6238888888889003</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Quimbaya+Quind%c3%ado&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.763055555555994</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>35276</fb>
-    <v>9</v>
-  </rv>
-  <rv s="9">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>e11d34ac-06ec-fddd-2922-bcc1256911ae</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>41</v>
-    <v>42</v>
-    <v>43</v>
-    <v>Quimbaya</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>44</v>
-    <v>Quimbaya es un municipio colombiano ubicado en la parte occidental del departamento del Quindío. Se encuentra a 20 km al noroeste de la capital del departamento, Armenia. Su nombre de la ciudad deriva de la cultura precolombina de la ...</v>
-    <v>71</v>
-    <v>117</v>
-    <v>118</v>
-    <v>119</v>
-    <v>120</v>
-    <v>Quimbaya</v>
-    <v>9</v>
-    <v>121</v>
-    <v>Quimbaya</v>
-    <v>mdp/vdpid/5580599568682188801</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Caldas</v>
-    <v>04477714-e978-8f38-f5a0-4812061eb226</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>133.4</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>12</v>
-    <v>7</v>
-    <v>45</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Caldas</v>
-  </rv>
-  <rv s="1">
-    <fb>6.0886111111111001</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Caldas+Antioquia&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Mauricio Cano Carmona (Alcalde)</v>
-    <v>e43f21fa-47d8-d579-476d-7a3920cf2fc8</v>
-    <v>es-ES</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>12</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.636111111111006</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>82234</fb>
-    <v>9</v>
-  </rv>
-  <rv s="10">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>04477714-e978-8f38-f5a0-4812061eb226</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>47</v>
-    <v>18</v>
-    <v>48</v>
-    <v>Caldas</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>20</v>
-    <v>124</v>
-    <v>Caldas es un municipio de Colombia, que está ubicado en el Valle de Aburrá del departamento de Antioquia. Limita por el norte con los municipios de La Estrella, Sabaneta y Envigado, por el este con el municipio de El Retiro, por el sur con los ...</v>
-    <v>2</v>
-    <v>2</v>
-    <v>125</v>
-    <v>126</v>
-    <v>127</v>
-    <v>129</v>
-    <v>130</v>
-    <v>Caldas</v>
-    <v>9</v>
-    <v>131</v>
-    <v>Caldas</v>
-    <v>mdp/vdpid/5577504301816741889</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>La Estrella</v>
-    <v>9c4a4ef2-2e3d-2eb2-b997-edd64bcbfe4e</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>35</fb>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>13</v>
-    <v>7</v>
-    <v>50</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of La Estrella</v>
-  </rv>
-  <rv s="1">
-    <fb>6.1561111111111</fb>
-    <v>10</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=La+Estrella+Antioquia&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>-75.641388888888997</fb>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <fb>71545</fb>
-    <v>9</v>
-  </rv>
-  <rv s="8">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>9c4a4ef2-2e3d-2eb2-b997-edd64bcbfe4e</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>51</v>
-    <v>2</v>
-    <v>33</v>
-    <v>La Estrella</v>
-    <v>5</v>
-    <v>6</v>
-    <v>Map</v>
-    <v>7</v>
-    <v>8</v>
-    <v>134</v>
-    <v>La Estrella, fundado como Nuestra Señora del Rosario de La Estrella, es un municipio de Colombia, ubicado en el Valle de Aburrá del departamento de Antioquia. Limita por el norte con los municipios de Medellín e Itagüí, por el este con los ...</v>
-    <v>2</v>
-    <v>135</v>
-    <v>136</v>
-    <v>137</v>
-    <v>138</v>
-    <v>La Estrella</v>
-    <v>9</v>
-    <v>139</v>
-    <v>La Estrella</v>
-    <v>mdp/vdpid/5577501281515208707</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
-  <s t="_linkedentity2">
-    <k n="%EntityServiceId" t="i"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="_Icon" t="s"/>
-  </s>
-  <s t="_formattednumber">
-    <k n="_Format" t="spb"/>
-  </s>
-  <s t="_webimage">
-    <k n="WebImageIdentifier" t="i"/>
-    <k n="_Provider" t="spb"/>
-    <k n="Attribution" t="spb"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="ComputedImage" t="b"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_hyperlink">
-    <k n="Address" t="s"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="`Área" t="r"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Líder(es)" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="`Área" t="r"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Líder(es)" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-    <k n="Zona(s) horaria(s)" t="r"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="`Área" t="r"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="División de administración 2 (condado/distrito/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Líder(es)" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-    <k n="Zona(s) horaria(s)" t="r"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="`Área" t="r"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-  </s>
-  <s t="_linkedentity2core">
-    <k n="_CRID" t="e"/>
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="_Attribution" t="spb"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_Provider" t="spb"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="`Área" t="r"/>
-    <k n="Descripción" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="r"/>
-    <k n="División de administración 2 (condado/distrito/otro)" t="r"/>
-    <k n="Imagen" t="r"/>
-    <k n="Latitud" t="r"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Líder(es)" t="r"/>
-    <k n="Longitud" t="r"/>
-    <k n="Nombre" t="s"/>
-    <k n="País o región" t="r"/>
-    <k n="Población" t="r"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="6">
-    <a count="26">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">Líder(es)</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">`Área</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-    <a count="27">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">Líder(es)</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">`Área</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">Zona(s) horaria(s)</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-    <a count="28">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 2 (condado/distrito/otro)</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">Líder(es)</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">`Área</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">Zona(s) horaria(s)</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-    <a count="25">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">`Área</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-    <a count="24">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-    <a count="27">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_Format</v>
-      <v t="s">División de administración 2 (condado/distrito/otro)</v>
-      <v t="s">División de administración 1 (estado/provincia/otro)</v>
-      <v t="s">País o región</v>
-      <v t="s">Líder(es)</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Población</v>
-      <v t="s">`Área</v>
-      <v t="s">Latitud</v>
-      <v t="s">Longitud</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Imagen</v>
-      <v t="s">Descripción</v>
-    </a>
-  </spbArrays>
-  <spbData count="52">
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Itag%C3%BC%C3%AD	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-    </spb>
-    <spb s="2">
-      <v>Area</v>
-      <v>Image</v>
-      <v>Name</v>
-      <v>Latitude</v>
-      <v>Longitude</v>
-      <v>Population</v>
-      <v>UniqueName</v>
-      <v>VDPID/VSID</v>
-      <v>Description</v>
-      <v>Country/region</v>
-      <v>LearnMoreOnLink</v>
-      <v>Admin Division 1 (State/province/other)</v>
-    </spb>
-    <spb s="3">
-      <v>0</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="4">
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-    </spb>
-    <spb s="5">
-      <v>4</v>
-      <v>4</v>
-      <v>4</v>
-    </spb>
-    <spb s="6">
-      <v>1</v>
-      <v>2</v>
-    </spb>
-    <spb s="7">
-      <v>https://www.bing.com</v>
-      <v>https://www.bing.com/th?id=Ga%5Cbing_yt.png&amp;w=100&amp;h=40&amp;c=0&amp;pid=0.1</v>
-      <v>Con tecnología de Bing</v>
-    </spb>
-    <spb s="8">
-      <v>kilómetro cuadrado</v>
-      <v>2018</v>
-    </spb>
-    <spb s="9">
-      <v>3</v>
-    </spb>
-    <spb s="9">
-      <v>4</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Envigado	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-    </spb>
-    <spb s="3">
-      <v>1</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Sabaneta_(Colombia)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-      <v>14</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/San_Antonio_(Texas)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="10">
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-      <v>16</v>
-    </spb>
-    <spb s="11">
-      <v>Area</v>
-      <v>Image</v>
-      <v>Name</v>
-      <v>Latitude</v>
-      <v>Longitude</v>
-      <v>Population</v>
-      <v>UniqueName</v>
-      <v>VDPID/VSID</v>
-      <v>Description</v>
-      <v>Country/region</v>
-      <v>LearnMoreOnLink</v>
-      <v>Admin Division 1 (State/province/other)</v>
-      <v>Admin Division 2 (County/district/other)</v>
-    </spb>
-    <spb s="3">
-      <v>2</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="8">
-      <v>kilómetro cuadrado</v>
-      <v>2020</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Medell%C3%ADn	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-      <v>21</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Pereira	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-      <v>23</v>
-    </spb>
-    <spb s="8">
-      <v>kilómetro cuadrado</v>
-      <v>2023</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Armenia_(Quind%C3%ADo)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-      <v>26</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Calarc%C3%A1_(Quind%C3%ADo)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-      <v>28</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Montenegro_(Quind%C3%ADo)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Montenegro,_Quindío	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="1">
-      <v>30</v>
-      <v>30</v>
-      <v>30</v>
-      <v>30</v>
-      <v>31</v>
-      <v>30</v>
-      <v>30</v>
-      <v>30</v>
-      <v>30</v>
-    </spb>
-    <spb s="3">
-      <v>3</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Circasia_(Quind%C3%ADo)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-      <v>34</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/La_Tebaida	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/La_Tebaida,_Quindío	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="1">
-      <v>36</v>
-      <v>36</v>
-      <v>36</v>
-      <v>36</v>
-      <v>37</v>
-      <v>36</v>
-      <v>36</v>
-      <v>36</v>
-      <v>36</v>
-    </spb>
-    <spb s="8">
-      <v>kilómetro cuadrado</v>
-      <v>2015</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Quimbaya_(Quind%C3%ADo)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="12">
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-      <v>40</v>
-    </spb>
-    <spb s="13">
-      <v>Image</v>
-      <v>Name</v>
-      <v>Latitude</v>
-      <v>Longitude</v>
-      <v>Population</v>
-      <v>UniqueName</v>
-      <v>VDPID/VSID</v>
-      <v>Description</v>
-      <v>Country/region</v>
-      <v>LearnMoreOnLink</v>
-      <v>Admin Division 1 (State/province/other)</v>
-    </spb>
-    <spb s="3">
-      <v>4</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="14">
-      <v>2018</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Caldas_(Antioquia)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Caldas,_Antioquia	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="10">
-      <v>45</v>
-      <v>45</v>
-      <v>45</v>
-      <v>45</v>
-      <v>46</v>
-      <v>45</v>
-      <v>45</v>
-      <v>45</v>
-      <v>45</v>
-      <v>45</v>
-    </spb>
-    <spb s="3">
-      <v>5</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/La_Estrella,_Antioquia	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/La_Estrella_(Antioquia)	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>49</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-      <v>50</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="15">
-  <s>
-    <k n="SourceText" t="s"/>
-    <k n="LicenseText" t="s"/>
-    <k n="SourceAddress" t="s"/>
-    <k n="LicenseAddress" t="s"/>
-  </s>
-  <s>
-    <k n="`Área" t="spb"/>
-    <k n="Nombre" t="spb"/>
-    <k n="Latitud" t="spb"/>
-    <k n="Longitud" t="spb"/>
-    <k n="Población" t="spb"/>
-    <k n="UniqueName" t="spb"/>
-    <k n="Descripción" t="spb"/>
-    <k n="País o región" t="spb"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="spb"/>
-  </s>
-  <s>
-    <k n="Área" t="s"/>
-    <k n="Imagen" t="s"/>
-    <k n="Nombre" t="s"/>
-    <k n="Latitud" t="s"/>
-    <k n="Longitud" t="s"/>
-    <k n="Población" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-    <k n="Descripción" t="s"/>
-    <k n="País o región" t="s"/>
-    <k n="LearnMoreOnLink" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="s"/>
-  </s>
-  <s>
-    <k n="^Order" t="spba"/>
-    <k n="TitleProperty" t="s"/>
-    <k n="SubTitleProperty" t="s"/>
-  </s>
-  <s>
-    <k n="ShowInCardView" t="b"/>
-    <k n="ShowInDotNotation" t="b"/>
-    <k n="ShowInAutoComplete" t="b"/>
-  </s>
-  <s>
-    <k n="UniqueName" t="spb"/>
-    <k n="VDPID/VSID" t="spb"/>
-    <k n="LearnMoreOnLink" t="spb"/>
-  </s>
-  <s>
-    <k n="Imagen" t="i"/>
-    <k n="Nombre" t="i"/>
-  </s>
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
-  </s>
-  <s>
-    <k n="`Área" t="s"/>
-    <k n="Población" t="s"/>
-  </s>
-  <s>
-    <k n="_Self" t="i"/>
-  </s>
-  <s>
-    <k n="`Área" t="spb"/>
-    <k n="Nombre" t="spb"/>
-    <k n="Latitud" t="spb"/>
-    <k n="Longitud" t="spb"/>
-    <k n="Población" t="spb"/>
-    <k n="UniqueName" t="spb"/>
-    <k n="Descripción" t="spb"/>
-    <k n="País o región" t="spb"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="spb"/>
-    <k n="División de administración 2 (condado/distrito/otro)" t="spb"/>
-  </s>
-  <s>
-    <k n="Área" t="s"/>
-    <k n="Imagen" t="s"/>
-    <k n="Nombre" t="s"/>
-    <k n="Latitud" t="s"/>
-    <k n="Longitud" t="s"/>
-    <k n="Población" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-    <k n="Descripción" t="s"/>
-    <k n="País o región" t="s"/>
-    <k n="LearnMoreOnLink" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="s"/>
-    <k n="División de administración 2 (condado/distrito/otro)" t="s"/>
-  </s>
-  <s>
-    <k n="Nombre" t="spb"/>
-    <k n="Latitud" t="spb"/>
-    <k n="Longitud" t="spb"/>
-    <k n="Población" t="spb"/>
-    <k n="UniqueName" t="spb"/>
-    <k n="Descripción" t="spb"/>
-    <k n="País o región" t="spb"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="spb"/>
-  </s>
-  <s>
-    <k n="Imagen" t="s"/>
-    <k n="Nombre" t="s"/>
-    <k n="Latitud" t="s"/>
-    <k n="Longitud" t="s"/>
-    <k n="Población" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="VDPID/VSID" t="s"/>
-    <k n="Descripción" t="s"/>
-    <k n="País o región" t="s"/>
-    <k n="LearnMoreOnLink" t="s"/>
-    <k n="División de administración 1 (estado/provincia/otro)" t="s"/>
-  </s>
-  <s>
-    <k n="Población" t="s"/>
-  </s>
-</spbStructures>
-</file>
-
-<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
-<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="2">
-    <x:dxf>
-      <x:numFmt numFmtId="3" formatCode="#,##0"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="0" formatCode="General"/>
-    </x:dxf>
-  </dxfs>
-  <richProperties>
-    <rPr n="IsHeroField" t="b"/>
-    <rPr n="IsTitleField" t="b"/>
-    <rPr n="NumberFormat" t="s"/>
-  </richProperties>
-  <richStyles>
-    <rSty>
-      <rpv i="0">1</rpv>
-    </rSty>
-    <rSty>
-      <rpv i="1">1</rpv>
-    </rSty>
-    <rSty dxfid="0">
-      <rpv i="2">#,##0</rpv>
-    </rSty>
-    <rSty dxfid="1">
-      <rpv i="2">0.0000</rpv>
-    </rSty>
-  </richStyles>
-</richStyleSheet>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}" name="DatosHogar" displayName="DatosHogar" ref="C2:X169" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
-  <autoFilter ref="C2:X169" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}"/>
+  <autoFilter ref="C2:X169" xr:uid="{861ED1CF-1DC9-4B50-80EC-BCE8066F9AFB}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Claro"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{FF7CD40D-656D-4CDC-993A-13C9C7E8DB40}" name="Operador" dataDxfId="39"/>
     <tableColumn id="16" xr3:uid="{E9D94F91-8BF6-49E6-A3A2-E88FE2FF45B1}" name="Ciudad" dataDxfId="38"/>
@@ -8150,7 +5788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>46091</v>
       </c>
@@ -8224,7 +5862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="43">
         <v>46091</v>
       </c>
@@ -8298,7 +5936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>46092</v>
       </c>
@@ -8364,7 +6002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="43">
         <v>46092</v>
       </c>
@@ -8432,7 +6070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <v>46092</v>
       </c>
@@ -8496,7 +6134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <v>46092</v>
       </c>
@@ -8560,7 +6198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <v>46092</v>
       </c>
@@ -8626,7 +6264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <v>46092</v>
       </c>
@@ -8692,7 +6330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>46092</v>
       </c>
@@ -8758,7 +6396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <v>46092</v>
       </c>
@@ -8824,7 +6462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <v>46092</v>
       </c>
@@ -8898,7 +6536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <v>46092</v>
       </c>
@@ -8972,7 +6610,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <v>46092</v>
       </c>
@@ -8982,8 +6620,8 @@
       <c r="C28" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D28" s="44" t="s">
+        <v>463</v>
       </c>
       <c r="E28" s="44" t="s">
         <v>41</v>
@@ -9044,7 +6682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <v>46092</v>
       </c>
@@ -9054,8 +6692,8 @@
       <c r="C29" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D29" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E29" s="44" t="s">
         <v>41</v>
@@ -9116,7 +6754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <v>46092</v>
       </c>
@@ -9126,8 +6764,8 @@
       <c r="C30" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D30" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E30" s="44" t="s">
         <v>41</v>
@@ -9188,7 +6826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="43">
         <v>46092</v>
       </c>
@@ -9198,8 +6836,8 @@
       <c r="C31" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D31" s="44" t="s">
+        <v>463</v>
       </c>
       <c r="E31" s="44" t="s">
         <v>41</v>
@@ -9260,7 +6898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43">
         <v>46092</v>
       </c>
@@ -9270,8 +6908,8 @@
       <c r="C32" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D32" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E32" s="44" t="s">
         <v>41</v>
@@ -9332,7 +6970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="43">
         <v>46092</v>
       </c>
@@ -9342,8 +6980,8 @@
       <c r="C33" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D33" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E33" s="44" t="s">
         <v>41</v>
@@ -9404,7 +7042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="43">
         <v>46092</v>
       </c>
@@ -9414,8 +7052,8 @@
       <c r="C34" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D34" s="44" t="s">
+        <v>463</v>
       </c>
       <c r="E34" s="44" t="s">
         <v>41</v>
@@ -9476,7 +7114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43">
         <v>46092</v>
       </c>
@@ -9486,8 +7124,8 @@
       <c r="C35" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D35" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>41</v>
@@ -9548,7 +7186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43">
         <v>46092</v>
       </c>
@@ -9558,8 +7196,8 @@
       <c r="C36" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D36" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>41</v>
@@ -9620,7 +7258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="43">
         <v>46092</v>
       </c>
@@ -9630,8 +7268,8 @@
       <c r="C37" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D37" s="44" t="s">
+        <v>463</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>41</v>
@@ -9692,7 +7330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="43">
         <v>46092</v>
       </c>
@@ -9702,8 +7340,8 @@
       <c r="C38" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D38" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E38" s="44" t="s">
         <v>41</v>
@@ -9764,7 +7402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43">
         <v>46092</v>
       </c>
@@ -9774,8 +7412,8 @@
       <c r="C39" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D39" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E39" s="44" t="s">
         <v>41</v>
@@ -9836,7 +7474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43">
         <v>46092</v>
       </c>
@@ -9846,8 +7484,8 @@
       <c r="C40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="44" t="e" vm="4">
-        <v>#VALUE!</v>
+      <c r="D40" s="44" t="s">
+        <v>464</v>
       </c>
       <c r="E40" s="44" t="s">
         <v>41</v>
@@ -9908,7 +7546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="43">
         <v>46092</v>
       </c>
@@ -9918,8 +7556,8 @@
       <c r="C41" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="44" t="e" vm="4">
-        <v>#VALUE!</v>
+      <c r="D41" s="44" t="s">
+        <v>464</v>
       </c>
       <c r="E41" s="44" t="s">
         <v>41</v>
@@ -9980,7 +7618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="43">
         <v>46092</v>
       </c>
@@ -9990,8 +7628,8 @@
       <c r="C42" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="44" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="D42" s="44" t="s">
+        <v>465</v>
       </c>
       <c r="E42" s="44" t="s">
         <v>41</v>
@@ -10052,7 +7690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="43">
         <v>46091</v>
       </c>
@@ -10062,8 +7700,8 @@
       <c r="C43" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="44" t="e" vm="6">
-        <v>#VALUE!</v>
+      <c r="D43" s="44" t="s">
+        <v>71</v>
       </c>
       <c r="E43" s="44" t="s">
         <v>28</v>
@@ -10118,7 +7756,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43">
         <v>46091</v>
       </c>
@@ -10128,8 +7766,8 @@
       <c r="C44" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="44" t="e" vm="6">
-        <v>#VALUE!</v>
+      <c r="D44" s="44" t="s">
+        <v>71</v>
       </c>
       <c r="E44" s="44" t="s">
         <v>28</v>
@@ -10187,7 +7825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43">
         <v>46091</v>
       </c>
@@ -10197,8 +7835,8 @@
       <c r="C45" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D45" s="44" t="e" vm="6">
-        <v>#VALUE!</v>
+      <c r="D45" s="44" t="s">
+        <v>71</v>
       </c>
       <c r="E45" s="44" t="s">
         <v>28</v>
@@ -10257,7 +7895,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43">
         <v>46092</v>
       </c>
@@ -10329,7 +7967,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43">
         <v>46092</v>
       </c>
@@ -10401,7 +8039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="48">
         <v>46091</v>
       </c>
@@ -10411,8 +8049,8 @@
       <c r="C48" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D48" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E48" s="44" t="s">
         <v>28</v>
@@ -10467,7 +8105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="48">
         <v>46091</v>
       </c>
@@ -10477,8 +8115,8 @@
       <c r="C49" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D49" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E49" s="44" t="s">
         <v>28</v>
@@ -10535,7 +8173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="48">
         <v>46091</v>
       </c>
@@ -10545,8 +8183,8 @@
       <c r="C50" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D50" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E50" s="44" t="s">
         <v>28</v>
@@ -10595,7 +8233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="48">
         <v>46091</v>
       </c>
@@ -10605,8 +8243,8 @@
       <c r="C51" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="44" t="e" vm="8">
-        <v>#VALUE!</v>
+      <c r="D51" s="44" t="s">
+        <v>466</v>
       </c>
       <c r="E51" s="44" t="s">
         <v>28</v>
@@ -10665,8 +8303,8 @@
       <c r="C52" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="44" t="e" vm="9">
-        <v>#VALUE!</v>
+      <c r="D52" s="44" t="s">
+        <v>70</v>
       </c>
       <c r="E52" s="44" t="s">
         <v>28</v>
@@ -10729,8 +8367,8 @@
       <c r="C53" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="44" t="e" vm="10">
-        <v>#VALUE!</v>
+      <c r="D53" s="44" t="s">
+        <v>58</v>
       </c>
       <c r="E53" s="44" t="s">
         <v>28</v>
@@ -10789,8 +8427,8 @@
       <c r="C54" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="44" t="e" vm="9">
-        <v>#VALUE!</v>
+      <c r="D54" s="44" t="s">
+        <v>70</v>
       </c>
       <c r="E54" s="44" t="s">
         <v>28</v>
@@ -10853,8 +8491,8 @@
       <c r="C55" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D55" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E55" s="77" t="s">
         <v>28</v>
@@ -10911,8 +8549,8 @@
       <c r="C56" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D56" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D56" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E56" s="77" t="s">
         <v>28</v>
@@ -10973,8 +8611,8 @@
       <c r="C57" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D57" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D57" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E57" s="77" t="s">
         <v>28</v>
@@ -11033,8 +8671,8 @@
       <c r="C58" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D58" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E58" s="77" t="s">
         <v>28</v>
@@ -11097,8 +8735,8 @@
       <c r="C59" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D59" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E59" s="77" t="s">
         <v>28</v>
@@ -11171,8 +8809,8 @@
       <c r="C60" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="77" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D60" s="77" t="s">
+        <v>27</v>
       </c>
       <c r="E60" s="77" t="s">
         <v>28</v>
@@ -11245,8 +8883,8 @@
       <c r="C61" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="77" t="e" vm="8">
-        <v>#VALUE!</v>
+      <c r="D61" s="77" t="s">
+        <v>466</v>
       </c>
       <c r="E61" s="77" t="s">
         <v>28</v>
@@ -11319,8 +8957,8 @@
       <c r="C62" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D62" s="77" t="e" vm="10">
-        <v>#VALUE!</v>
+      <c r="D62" s="77" t="s">
+        <v>58</v>
       </c>
       <c r="E62" s="77" t="s">
         <v>28</v>
@@ -11537,8 +9175,8 @@
       <c r="C65" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D65" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E65" s="44" t="s">
         <v>28</v>
@@ -11605,8 +9243,8 @@
       <c r="C66" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D66" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E66" s="44" t="s">
         <v>28</v>
@@ -11665,8 +9303,8 @@
       <c r="C67" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="44" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D67" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="E67" s="44" t="s">
         <v>28</v>
@@ -11731,8 +9369,8 @@
       <c r="C68" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D68" s="78" t="e" vm="11">
-        <v>#VALUE!</v>
+      <c r="D68" s="78" t="s">
+        <v>467</v>
       </c>
       <c r="E68" s="50" t="s">
         <v>28</v>
@@ -11795,8 +9433,8 @@
       <c r="C69" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="78" t="e" vm="11">
-        <v>#VALUE!</v>
+      <c r="D69" s="78" t="s">
+        <v>467</v>
       </c>
       <c r="E69" s="50" t="s">
         <v>28</v>
@@ -11855,8 +9493,8 @@
       <c r="C70" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="78" t="e" vm="12">
-        <v>#VALUE!</v>
+      <c r="D70" s="78" t="s">
+        <v>72</v>
       </c>
       <c r="E70" s="50" t="s">
         <v>28</v>
@@ -11919,8 +9557,8 @@
       <c r="C71" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="78" t="e" vm="12">
-        <v>#VALUE!</v>
+      <c r="D71" s="78" t="s">
+        <v>72</v>
       </c>
       <c r="E71" s="50" t="s">
         <v>28</v>
@@ -11979,8 +9617,8 @@
       <c r="C72" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D72" s="78" t="e" vm="12">
-        <v>#VALUE!</v>
+      <c r="D72" s="78" t="s">
+        <v>72</v>
       </c>
       <c r="E72" s="50" t="s">
         <v>28</v>
@@ -12053,8 +9691,8 @@
       <c r="C73" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="78" t="e" vm="11">
-        <v>#VALUE!</v>
+      <c r="D73" s="78" t="s">
+        <v>467</v>
       </c>
       <c r="E73" s="50" t="s">
         <v>28</v>
@@ -12127,8 +9765,8 @@
       <c r="C74" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="78" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="D74" s="78" t="s">
+        <v>27</v>
       </c>
       <c r="E74" s="50" t="s">
         <v>28</v>
@@ -12201,8 +9839,8 @@
       <c r="C75" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="50" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="D75" s="50" t="s">
+        <v>465</v>
       </c>
       <c r="E75" s="50" t="s">
         <v>41</v>
@@ -12259,7 +9897,7 @@
       <c r="W75" s="51"/>
       <c r="X75" s="51"/>
     </row>
-    <row r="76" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43">
         <v>46092</v>
       </c>
@@ -12269,8 +9907,8 @@
       <c r="C76" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D76" s="44" t="s">
+        <v>463</v>
       </c>
       <c r="E76" s="44" t="s">
         <v>41</v>
@@ -12339,8 +9977,8 @@
       <c r="C77" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D77" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D77" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E77" s="50" t="s">
         <v>41</v>
@@ -12413,8 +10051,8 @@
       <c r="C78" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D78" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D78" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E78" s="50" t="s">
         <v>41</v>
@@ -12487,8 +10125,8 @@
       <c r="C79" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="50" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="D79" s="50" t="s">
+        <v>465</v>
       </c>
       <c r="E79" s="50" t="s">
         <v>41</v>
@@ -12559,8 +10197,8 @@
       <c r="C80" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D80" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E80" s="50" t="s">
         <v>41</v>
@@ -12631,8 +10269,8 @@
       <c r="C81" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D81" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D81" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E81" s="50" t="s">
         <v>41</v>
@@ -12705,8 +10343,8 @@
       <c r="C82" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D82" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D82" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E82" s="50" t="s">
         <v>41</v>
@@ -12779,8 +10417,8 @@
       <c r="C83" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D83" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D83" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E83" s="50" t="s">
         <v>41</v>
@@ -12888,8 +10526,8 @@
       <c r="C85" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D85" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E85" s="50" t="s">
         <v>41</v>
@@ -12962,8 +10600,8 @@
       <c r="C86" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D86" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E86" s="50" t="s">
         <v>41</v>
@@ -13036,8 +10674,8 @@
       <c r="C87" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D87" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E87" s="50" t="s">
         <v>41</v>
@@ -13110,8 +10748,8 @@
       <c r="C88" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D88" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E88" s="50" t="s">
         <v>41</v>
@@ -13184,8 +10822,8 @@
       <c r="C89" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D89" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D89" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E89" s="50" t="s">
         <v>41</v>
@@ -13258,8 +10896,8 @@
       <c r="C90" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D90" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E90" s="50" t="s">
         <v>41</v>
@@ -13332,8 +10970,8 @@
       <c r="C91" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D91" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D91" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E91" s="50" t="s">
         <v>41</v>
@@ -13406,8 +11044,8 @@
       <c r="C92" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D92" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E92" s="50" t="s">
         <v>41</v>
@@ -13480,8 +11118,8 @@
       <c r="C93" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D93" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D93" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E93" s="50" t="s">
         <v>41</v>
@@ -13554,8 +11192,8 @@
       <c r="C94" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D94" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D94" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E94" s="50" t="s">
         <v>41</v>
@@ -13628,8 +11266,8 @@
       <c r="C95" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="50" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D95" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="E95" s="50" t="s">
         <v>41</v>
@@ -13702,8 +11340,8 @@
       <c r="C96" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="44" t="e" vm="13">
-        <v>#VALUE!</v>
+      <c r="D96" s="44" t="s">
+        <v>56</v>
       </c>
       <c r="E96" s="44" t="s">
         <v>41</v>
@@ -13776,8 +11414,8 @@
       <c r="C97" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D97" s="44" t="e" vm="14">
-        <v>#VALUE!</v>
+      <c r="D97" s="44" t="s">
+        <v>66</v>
       </c>
       <c r="E97" s="44" t="s">
         <v>41</v>
@@ -13848,8 +11486,8 @@
       <c r="C98" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D98" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D98" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E98" s="44" t="s">
         <v>41</v>
@@ -13922,8 +11560,8 @@
       <c r="C99" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D99" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E99" s="44" t="s">
         <v>41</v>
@@ -13996,8 +11634,8 @@
       <c r="C100" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D100" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E100" s="44" t="s">
         <v>41</v>
@@ -14070,8 +11708,8 @@
       <c r="C101" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D101" s="44" t="e" vm="13">
-        <v>#VALUE!</v>
+      <c r="D101" s="44" t="s">
+        <v>56</v>
       </c>
       <c r="E101" s="44" t="s">
         <v>41</v>
@@ -14144,8 +11782,8 @@
       <c r="C102" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D102" s="44" t="e" vm="13">
-        <v>#VALUE!</v>
+      <c r="D102" s="44" t="s">
+        <v>56</v>
       </c>
       <c r="E102" s="44" t="s">
         <v>41</v>
@@ -14218,8 +11856,8 @@
       <c r="C103" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D103" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D103" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E103" s="44" t="s">
         <v>41</v>
@@ -14292,8 +11930,8 @@
       <c r="C104" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D104" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D104" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E104" s="44" t="s">
         <v>41</v>
@@ -14366,8 +12004,8 @@
       <c r="C105" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="44" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="D105" s="44" t="s">
+        <v>74</v>
       </c>
       <c r="E105" s="44" t="s">
         <v>41</v>
@@ -14440,8 +12078,8 @@
       <c r="C106" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D106" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E106" s="44" t="s">
         <v>41</v>
@@ -14514,8 +12152,8 @@
       <c r="C107" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D107" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E107" s="44" t="s">
         <v>41</v>
@@ -14588,8 +12226,8 @@
       <c r="C108" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D108" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D108" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E108" s="44" t="s">
         <v>41</v>
@@ -14662,8 +12300,8 @@
       <c r="C109" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D109" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D109" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E109" s="44" t="s">
         <v>41</v>
@@ -14736,8 +12374,8 @@
       <c r="C110" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D110" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D110" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E110" s="44" t="s">
         <v>41</v>
@@ -14810,8 +12448,8 @@
       <c r="C111" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D111" s="44" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="D111" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E111" s="44" t="s">
         <v>41</v>
@@ -14884,8 +12522,8 @@
       <c r="C112" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D112" s="44" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="D112" s="44" t="s">
+        <v>465</v>
       </c>
       <c r="E112" s="44" t="s">
         <v>41</v>
@@ -14958,8 +12596,8 @@
       <c r="C113" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D113" s="44" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="D113" s="44" t="s">
+        <v>465</v>
       </c>
       <c r="E113" s="44" t="s">
         <v>41</v>
@@ -15022,7 +12660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="43">
         <v>46092</v>
       </c>
@@ -15096,7 +12734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="43">
         <v>46092</v>
       </c>
@@ -15170,7 +12808,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="43">
         <v>46092</v>
       </c>
@@ -15244,7 +12882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="43">
         <v>46092</v>
       </c>
@@ -15318,7 +12956,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="43">
         <v>46092</v>
       </c>
@@ -15392,7 +13030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="43">
         <v>46092</v>
       </c>
@@ -15466,7 +13104,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="43">
         <v>46092</v>
       </c>
@@ -15540,7 +13178,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="43">
         <v>46092</v>
       </c>
@@ -15614,7 +13252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:24" s="45" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:24" s="45" customFormat="1" ht="75.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="43">
         <v>46092</v>
       </c>
@@ -15688,7 +13326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="62"/>
       <c r="B123" s="63"/>
       <c r="C123" s="64"/>
@@ -15717,7 +13355,7 @@
       <c r="W123" s="65"/>
       <c r="X123" s="65"/>
     </row>
-    <row r="124" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="69"/>
       <c r="B124" s="70"/>
       <c r="C124" s="71"/>
@@ -15746,7 +13384,7 @@
       <c r="W124" s="72"/>
       <c r="X124" s="65"/>
     </row>
-    <row r="125" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="69"/>
       <c r="B125" s="70"/>
       <c r="C125" s="71"/>
@@ -15775,7 +13413,7 @@
       <c r="W125" s="72"/>
       <c r="X125" s="65"/>
     </row>
-    <row r="126" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="69"/>
       <c r="B126" s="70"/>
       <c r="C126" s="71"/>
@@ -15804,7 +13442,7 @@
       <c r="W126" s="72"/>
       <c r="X126" s="65"/>
     </row>
-    <row r="127" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="69"/>
       <c r="B127" s="70"/>
       <c r="C127" s="71"/>
@@ -15833,7 +13471,7 @@
       <c r="W127" s="72"/>
       <c r="X127" s="65"/>
     </row>
-    <row r="128" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="69"/>
       <c r="B128" s="70"/>
       <c r="C128" s="71"/>
@@ -15862,7 +13500,7 @@
       <c r="W128" s="72"/>
       <c r="X128" s="65"/>
     </row>
-    <row r="129" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="69"/>
       <c r="B129" s="70"/>
       <c r="C129" s="71"/>
@@ -15891,7 +13529,7 @@
       <c r="W129" s="72"/>
       <c r="X129" s="65"/>
     </row>
-    <row r="130" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="69"/>
       <c r="B130" s="70"/>
       <c r="C130" s="71"/>
@@ -15920,7 +13558,7 @@
       <c r="W130" s="72"/>
       <c r="X130" s="65"/>
     </row>
-    <row r="131" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="69"/>
       <c r="B131" s="70"/>
       <c r="C131" s="71"/>
@@ -15949,7 +13587,7 @@
       <c r="W131" s="72"/>
       <c r="X131" s="65"/>
     </row>
-    <row r="132" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="69"/>
       <c r="B132" s="70"/>
       <c r="C132" s="71"/>
@@ -15978,7 +13616,7 @@
       <c r="W132" s="72"/>
       <c r="X132" s="65"/>
     </row>
-    <row r="133" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="69"/>
       <c r="B133" s="70"/>
       <c r="C133" s="71"/>
@@ -16007,7 +13645,7 @@
       <c r="W133" s="72"/>
       <c r="X133" s="65"/>
     </row>
-    <row r="134" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="69"/>
       <c r="B134" s="70"/>
       <c r="C134" s="71"/>
@@ -16036,7 +13674,7 @@
       <c r="W134" s="72"/>
       <c r="X134" s="65"/>
     </row>
-    <row r="135" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="69"/>
       <c r="B135" s="70"/>
       <c r="C135" s="71"/>
@@ -16065,7 +13703,7 @@
       <c r="W135" s="72"/>
       <c r="X135" s="65"/>
     </row>
-    <row r="136" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="69"/>
       <c r="B136" s="70"/>
       <c r="C136" s="71"/>
@@ -16094,7 +13732,7 @@
       <c r="W136" s="72"/>
       <c r="X136" s="65"/>
     </row>
-    <row r="137" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="69"/>
       <c r="B137" s="70"/>
       <c r="C137" s="71"/>
@@ -16123,7 +13761,7 @@
       <c r="W137" s="72"/>
       <c r="X137" s="65"/>
     </row>
-    <row r="138" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="69"/>
       <c r="B138" s="70"/>
       <c r="C138" s="71"/>
@@ -16152,7 +13790,7 @@
       <c r="W138" s="72"/>
       <c r="X138" s="65"/>
     </row>
-    <row r="139" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="69"/>
       <c r="B139" s="70"/>
       <c r="C139" s="71"/>
@@ -16181,7 +13819,7 @@
       <c r="W139" s="72"/>
       <c r="X139" s="65"/>
     </row>
-    <row r="140" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="69"/>
       <c r="B140" s="70"/>
       <c r="C140" s="71"/>
@@ -16210,7 +13848,7 @@
       <c r="W140" s="72"/>
       <c r="X140" s="65"/>
     </row>
-    <row r="141" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="69"/>
       <c r="B141" s="70"/>
       <c r="C141" s="71"/>
@@ -16239,7 +13877,7 @@
       <c r="W141" s="72"/>
       <c r="X141" s="65"/>
     </row>
-    <row r="142" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="69"/>
       <c r="B142" s="70"/>
       <c r="C142" s="71"/>
@@ -16268,7 +13906,7 @@
       <c r="W142" s="72"/>
       <c r="X142" s="65"/>
     </row>
-    <row r="143" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="69"/>
       <c r="B143" s="70"/>
       <c r="C143" s="71"/>
@@ -16297,7 +13935,7 @@
       <c r="W143" s="72"/>
       <c r="X143" s="65"/>
     </row>
-    <row r="144" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="69"/>
       <c r="B144" s="70"/>
       <c r="C144" s="71"/>
@@ -16326,7 +13964,7 @@
       <c r="W144" s="72"/>
       <c r="X144" s="65"/>
     </row>
-    <row r="145" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="69"/>
       <c r="B145" s="70"/>
       <c r="C145" s="71"/>
@@ -16355,7 +13993,7 @@
       <c r="W145" s="72"/>
       <c r="X145" s="65"/>
     </row>
-    <row r="146" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="69"/>
       <c r="B146" s="70"/>
       <c r="C146" s="71"/>
@@ -16384,7 +14022,7 @@
       <c r="W146" s="72"/>
       <c r="X146" s="65"/>
     </row>
-    <row r="147" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="69"/>
       <c r="B147" s="70"/>
       <c r="C147" s="71"/>
@@ -16413,7 +14051,7 @@
       <c r="W147" s="72"/>
       <c r="X147" s="65"/>
     </row>
-    <row r="148" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="69"/>
       <c r="B148" s="70"/>
       <c r="C148" s="71"/>
@@ -16442,7 +14080,7 @@
       <c r="W148" s="72"/>
       <c r="X148" s="65"/>
     </row>
-    <row r="149" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="69"/>
       <c r="B149" s="70"/>
       <c r="C149" s="71"/>
@@ -16471,7 +14109,7 @@
       <c r="W149" s="72"/>
       <c r="X149" s="65"/>
     </row>
-    <row r="150" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="69"/>
       <c r="B150" s="70"/>
       <c r="C150" s="71"/>
@@ -16500,7 +14138,7 @@
       <c r="W150" s="72"/>
       <c r="X150" s="65"/>
     </row>
-    <row r="151" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="69"/>
       <c r="B151" s="70"/>
       <c r="C151" s="71"/>
@@ -16529,7 +14167,7 @@
       <c r="W151" s="72"/>
       <c r="X151" s="65"/>
     </row>
-    <row r="152" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="69"/>
       <c r="B152" s="70"/>
       <c r="C152" s="71"/>
@@ -16558,7 +14196,7 @@
       <c r="W152" s="72"/>
       <c r="X152" s="65"/>
     </row>
-    <row r="153" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="69"/>
       <c r="B153" s="70"/>
       <c r="C153" s="71"/>
@@ -16587,7 +14225,7 @@
       <c r="W153" s="72"/>
       <c r="X153" s="65"/>
     </row>
-    <row r="154" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="69"/>
       <c r="B154" s="70"/>
       <c r="C154" s="71"/>
@@ -16616,7 +14254,7 @@
       <c r="W154" s="72"/>
       <c r="X154" s="65"/>
     </row>
-    <row r="155" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="69"/>
       <c r="B155" s="70"/>
       <c r="C155" s="71"/>
@@ -16645,7 +14283,7 @@
       <c r="W155" s="72"/>
       <c r="X155" s="65"/>
     </row>
-    <row r="156" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="69"/>
       <c r="B156" s="70"/>
       <c r="C156" s="71"/>
@@ -16674,7 +14312,7 @@
       <c r="W156" s="72"/>
       <c r="X156" s="65"/>
     </row>
-    <row r="157" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="69"/>
       <c r="B157" s="70"/>
       <c r="C157" s="71"/>
@@ -16703,7 +14341,7 @@
       <c r="W157" s="72"/>
       <c r="X157" s="65"/>
     </row>
-    <row r="158" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="69"/>
       <c r="B158" s="70"/>
       <c r="C158" s="71"/>
@@ -16732,7 +14370,7 @@
       <c r="W158" s="72"/>
       <c r="X158" s="65"/>
     </row>
-    <row r="159" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="69"/>
       <c r="B159" s="70"/>
       <c r="C159" s="71"/>
@@ -16761,7 +14399,7 @@
       <c r="W159" s="72"/>
       <c r="X159" s="65"/>
     </row>
-    <row r="160" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="69"/>
       <c r="B160" s="70"/>
       <c r="C160" s="71"/>
@@ -16790,7 +14428,7 @@
       <c r="W160" s="72"/>
       <c r="X160" s="65"/>
     </row>
-    <row r="161" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="69"/>
       <c r="B161" s="70"/>
       <c r="C161" s="71"/>
@@ -16819,7 +14457,7 @@
       <c r="W161" s="72"/>
       <c r="X161" s="65"/>
     </row>
-    <row r="162" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="69"/>
       <c r="B162" s="70"/>
       <c r="C162" s="71"/>
@@ -16848,7 +14486,7 @@
       <c r="W162" s="72"/>
       <c r="X162" s="65"/>
     </row>
-    <row r="163" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="69"/>
       <c r="B163" s="70"/>
       <c r="C163" s="71"/>
@@ -16877,7 +14515,7 @@
       <c r="W163" s="72"/>
       <c r="X163" s="65"/>
     </row>
-    <row r="164" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="69"/>
       <c r="B164" s="70"/>
       <c r="C164" s="71"/>
@@ -16906,7 +14544,7 @@
       <c r="W164" s="72"/>
       <c r="X164" s="65"/>
     </row>
-    <row r="165" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="69"/>
       <c r="B165" s="70"/>
       <c r="C165" s="71"/>
@@ -16935,7 +14573,7 @@
       <c r="W165" s="72"/>
       <c r="X165" s="65"/>
     </row>
-    <row r="166" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="69"/>
       <c r="B166" s="70"/>
       <c r="C166" s="71"/>
@@ -16964,7 +14602,7 @@
       <c r="W166" s="72"/>
       <c r="X166" s="65"/>
     </row>
-    <row r="167" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="69"/>
       <c r="B167" s="70"/>
       <c r="C167" s="71"/>
@@ -16993,7 +14631,7 @@
       <c r="W167" s="72"/>
       <c r="X167" s="65"/>
     </row>
-    <row r="168" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="69"/>
       <c r="B168" s="70"/>
       <c r="C168" s="71"/>
@@ -17022,7 +14660,7 @@
       <c r="W168" s="72"/>
       <c r="X168" s="65"/>
     </row>
-    <row r="169" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:24" s="68" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="69"/>
       <c r="B169" s="70"/>
       <c r="C169" s="71"/>
@@ -21499,7 +19137,7 @@
         <v>300</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D66" s="37">
         <v>2380</v>
@@ -21805,6 +19443,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008132F03F7BAE544691E1D8ED0BBAB87D" ma:contentTypeVersion="21" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e484fd9c9d78115df5d140a0e15bddb5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="612f0692-a35d-4227-ae2b-09b69c7561dc" xmlns:ns3="c9fa2ff5-4241-4755-bdec-11c5f369898d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60915895e4af9a5e40828d772a1103ab" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -22082,30 +19743,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
+    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="c9fa2ff5-4241-4755-bdec-11c5f369898d" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Modificaci_x00f3_n xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="612f0692-a35d-4227-ae2b-09b69c7561dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B03BB360-2000-407D-9849-F3FC94EAD1FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22123,24 +19781,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40ABE366-40E8-4826-A3F5-1FFD3933E216}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23710A79-796B-4747-B42A-CDF5DE71A590}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="c9fa2ff5-4241-4755-bdec-11c5f369898d"/>
-    <ds:schemaRef ds:uri="612f0692-a35d-4227-ae2b-09b69c7561dc"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>